--- a/Bert Map/size_proportions_by_channel_gender.xlsx
+++ b/Bert Map/size_proportions_by_channel_gender.xlsx
@@ -483,22 +483,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.87160674981658</v>
+        <v>25.00924651414532</v>
       </c>
       <c r="E2" t="n">
-        <v>32.72193690388848</v>
+        <v>32.53092934825833</v>
       </c>
       <c r="F2" t="n">
-        <v>15.11371973587674</v>
+        <v>14.98958044903949</v>
       </c>
       <c r="G2" t="n">
-        <v>11.00513573000734</v>
+        <v>11.74178310958193</v>
       </c>
       <c r="H2" t="n">
-        <v>9.024211298606016</v>
+        <v>8.742180308904246</v>
       </c>
       <c r="I2" t="n">
-        <v>7.263389581804843</v>
+        <v>6.986280270070684</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -519,25 +519,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.343409915356711</v>
+        <v>8.072009074588216</v>
       </c>
       <c r="E3" t="n">
-        <v>12.57557436517533</v>
+        <v>12.30738715769581</v>
       </c>
       <c r="F3" t="n">
-        <v>22.49093107617896</v>
+        <v>22.97173185026243</v>
       </c>
       <c r="G3" t="n">
-        <v>4.71584038694075</v>
+        <v>4.637377101406429</v>
       </c>
       <c r="H3" t="n">
-        <v>32.88996372430471</v>
+        <v>33.13156903616895</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>18.98428053204353</v>
+        <v>18.87992577987817</v>
       </c>
     </row>
     <row r="4">
@@ -555,22 +555,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.18047337278107</v>
+        <v>27.7219567891732</v>
       </c>
       <c r="E4" t="n">
-        <v>29.95562130177515</v>
+        <v>30.31117647248511</v>
       </c>
       <c r="F4" t="n">
-        <v>13.53550295857988</v>
+        <v>13.6474868835063</v>
       </c>
       <c r="G4" t="n">
-        <v>13.31360946745562</v>
+        <v>13.60982103619547</v>
       </c>
       <c r="H4" t="n">
-        <v>8.210059171597633</v>
+        <v>8.118435844988129</v>
       </c>
       <c r="I4" t="n">
-        <v>6.804733727810651</v>
+        <v>6.591122973651782</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -591,25 +591,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.004830917874397</v>
+        <v>6.977999787378451</v>
       </c>
       <c r="E5" t="n">
-        <v>9.420289855072465</v>
+        <v>9.754066474392161</v>
       </c>
       <c r="F5" t="n">
-        <v>25.48309178743962</v>
+        <v>25.41342991602419</v>
       </c>
       <c r="G5" t="n">
-        <v>4.347826086956522</v>
+        <v>4.333185592503388</v>
       </c>
       <c r="H5" t="n">
-        <v>35.26570048309179</v>
+        <v>34.81134332892483</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>18.47826086956522</v>
+        <v>18.70997490077696</v>
       </c>
     </row>
     <row r="6">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.39608338597599</v>
+        <v>30.22723352481495</v>
       </c>
       <c r="E6" t="n">
-        <v>24.88945041061276</v>
+        <v>26.23262765276497</v>
       </c>
       <c r="F6" t="n">
-        <v>15.28742893240682</v>
+        <v>15.1350019217388</v>
       </c>
       <c r="G6" t="n">
-        <v>11.62349968414403</v>
+        <v>12.27180518606762</v>
       </c>
       <c r="H6" t="n">
-        <v>10.23373341756159</v>
+        <v>9.733223787029678</v>
       </c>
       <c r="I6" t="n">
-        <v>6.5698041692988</v>
+        <v>6.400107927583999</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -663,25 +663,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.349206349206349</v>
+        <v>6.378783773586432</v>
       </c>
       <c r="E7" t="n">
-        <v>11.77248677248677</v>
+        <v>11.62910767004825</v>
       </c>
       <c r="F7" t="n">
-        <v>28.96825396825397</v>
+        <v>28.32005855959407</v>
       </c>
       <c r="G7" t="n">
-        <v>5.026455026455026</v>
+        <v>4.936079082826127</v>
       </c>
       <c r="H7" t="n">
-        <v>29.1005291005291</v>
+        <v>29.86583418255676</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>18.78306878306878</v>
+        <v>18.87013673138835</v>
       </c>
     </row>
     <row r="8">
@@ -699,22 +699,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24.34733257661748</v>
+        <v>24.51859754408002</v>
       </c>
       <c r="E8" t="n">
-        <v>29.28490351872871</v>
+        <v>29.95608158143565</v>
       </c>
       <c r="F8" t="n">
-        <v>16.23155505107832</v>
+        <v>15.7789414657194</v>
       </c>
       <c r="G8" t="n">
-        <v>14.47219069239501</v>
+        <v>14.57275423440026</v>
       </c>
       <c r="H8" t="n">
-        <v>8.51305334846765</v>
+        <v>8.287408859707668</v>
       </c>
       <c r="I8" t="n">
-        <v>7.150964812712826</v>
+        <v>6.886216314656996</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -735,25 +735,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.521739130434782</v>
+        <v>6.598344224262517</v>
       </c>
       <c r="E9" t="n">
-        <v>12.70022883295195</v>
+        <v>12.40240108537039</v>
       </c>
       <c r="F9" t="n">
-        <v>25.62929061784897</v>
+        <v>25.51922665143342</v>
       </c>
       <c r="G9" t="n">
-        <v>4.919908466819222</v>
+        <v>4.835253143469409</v>
       </c>
       <c r="H9" t="n">
-        <v>31.57894736842105</v>
+        <v>31.84381596771906</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>18.64988558352403</v>
+        <v>18.80095892774521</v>
       </c>
     </row>
     <row r="10">
@@ -771,22 +771,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.42569567791593</v>
+        <v>28.45710810366583</v>
       </c>
       <c r="E10" t="n">
-        <v>29.36648904677324</v>
+        <v>30.09929044745229</v>
       </c>
       <c r="F10" t="n">
-        <v>13.55831853167555</v>
+        <v>13.69184051896546</v>
       </c>
       <c r="G10" t="n">
-        <v>12.96625222024867</v>
+        <v>13.40043703480046</v>
       </c>
       <c r="H10" t="n">
-        <v>7.223208999407933</v>
+        <v>7.183188270094225</v>
       </c>
       <c r="I10" t="n">
-        <v>7.460035523978685</v>
+        <v>7.168135625021719</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -807,25 +807,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.549132947976879</v>
+        <v>5.760821761161916</v>
       </c>
       <c r="E11" t="n">
-        <v>14.33526011560694</v>
+        <v>13.80817859236682</v>
       </c>
       <c r="F11" t="n">
-        <v>25.20231213872832</v>
+        <v>25.25282518711957</v>
       </c>
       <c r="G11" t="n">
-        <v>4.855491329479769</v>
+        <v>4.780153454189417</v>
       </c>
       <c r="H11" t="n">
-        <v>32.83236994219653</v>
+        <v>32.74601911872984</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>17.22543352601156</v>
+        <v>17.65200188643244</v>
       </c>
     </row>
     <row r="12">
@@ -843,22 +843,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>24.63193657984145</v>
+        <v>24.68918272705385</v>
       </c>
       <c r="E12" t="n">
-        <v>37.88221970554926</v>
+        <v>36.97365838311718</v>
       </c>
       <c r="F12" t="n">
-        <v>14.94903737259343</v>
+        <v>14.83522049253123</v>
       </c>
       <c r="G12" t="n">
-        <v>10.87202718006795</v>
+        <v>11.56238819963145</v>
       </c>
       <c r="H12" t="n">
-        <v>7.078142695356739</v>
+        <v>7.14033938292921</v>
       </c>
       <c r="I12" t="n">
-        <v>4.586636466591167</v>
+        <v>4.799210814737062</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -879,25 +879,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>5.81039755351682</v>
+        <v>6.001867082565441</v>
       </c>
       <c r="E13" t="n">
-        <v>12.43628950050968</v>
+        <v>12.27281644640665</v>
       </c>
       <c r="F13" t="n">
-        <v>24.56676860346585</v>
+        <v>24.5360577672919</v>
       </c>
       <c r="G13" t="n">
-        <v>5.198776758409786</v>
+        <v>5.022018048227209</v>
       </c>
       <c r="H13" t="n">
-        <v>31.70234454638124</v>
+        <v>32.02407673092299</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>20.28542303771662</v>
+        <v>20.14316392458581</v>
       </c>
     </row>
     <row r="14">
@@ -915,22 +915,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>26.06294864715627</v>
+        <v>25.84244747228167</v>
       </c>
       <c r="E14" t="n">
-        <v>30.31474323578134</v>
+        <v>30.71492919000733</v>
       </c>
       <c r="F14" t="n">
-        <v>17.06239646604086</v>
+        <v>16.66699129838286</v>
       </c>
       <c r="G14" t="n">
-        <v>12.53451131971287</v>
+        <v>12.98891729280444</v>
       </c>
       <c r="H14" t="n">
-        <v>7.123136388735506</v>
+        <v>7.13296846675246</v>
       </c>
       <c r="I14" t="n">
-        <v>6.902263942573164</v>
+        <v>6.653746279771246</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7.823960880195599</v>
+        <v>7.565758316694289</v>
       </c>
       <c r="E15" t="n">
-        <v>13.32518337408313</v>
+        <v>13.0235189114346</v>
       </c>
       <c r="F15" t="n">
-        <v>25.55012224938875</v>
+        <v>25.50419065113778</v>
       </c>
       <c r="G15" t="n">
-        <v>4.278728606356968</v>
+        <v>4.275163004259906</v>
       </c>
       <c r="H15" t="n">
-        <v>29.09535452322739</v>
+        <v>29.77396343632342</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>19.92665036674817</v>
+        <v>19.85740568015001</v>
       </c>
     </row>
     <row r="16">
@@ -987,22 +987,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>24.90185081323612</v>
+        <v>24.86015189987345</v>
       </c>
       <c r="E16" t="n">
-        <v>29.33258553000561</v>
+        <v>29.99133078205325</v>
       </c>
       <c r="F16" t="n">
-        <v>17.04991587212563</v>
+        <v>16.60587920541768</v>
       </c>
       <c r="G16" t="n">
-        <v>11.55356141334829</v>
+        <v>12.14099456823617</v>
       </c>
       <c r="H16" t="n">
-        <v>8.749298934380258</v>
+        <v>8.427002260130976</v>
       </c>
       <c r="I16" t="n">
-        <v>8.412787436904095</v>
+        <v>7.974641284288459</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1023,25 +1023,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7.864164432529044</v>
+        <v>7.658820989468115</v>
       </c>
       <c r="E17" t="n">
-        <v>12.24307417336908</v>
+        <v>11.89901847552178</v>
       </c>
       <c r="F17" t="n">
-        <v>24.30741733690795</v>
+        <v>24.36572191055277</v>
       </c>
       <c r="G17" t="n">
-        <v>3.753351206434316</v>
+        <v>3.827709134183573</v>
       </c>
       <c r="H17" t="n">
-        <v>33.69079535299375</v>
+        <v>33.77883883824903</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>18.14119749776586</v>
+        <v>18.46989065202474</v>
       </c>
     </row>
     <row r="18">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.54076539101498</v>
+        <v>25.76113609643298</v>
       </c>
       <c r="E18" t="n">
-        <v>30.61564059900167</v>
+        <v>30.55630527608501</v>
       </c>
       <c r="F18" t="n">
-        <v>15.3910149750416</v>
+        <v>15.18961197525804</v>
       </c>
       <c r="G18" t="n">
-        <v>11.98003327787022</v>
+        <v>11.92255830380178</v>
       </c>
       <c r="H18" t="n">
-        <v>8.735440931780367</v>
+        <v>8.969885749945664</v>
       </c>
       <c r="I18" t="n">
-        <v>7.737104825291182</v>
+        <v>7.600502598476528</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1095,25 +1095,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.777166437414031</v>
+        <v>5.871489736161362</v>
       </c>
       <c r="E19" t="n">
-        <v>12.5171939477304</v>
+        <v>12.18817725587569</v>
       </c>
       <c r="F19" t="n">
-        <v>26.82255845942229</v>
+        <v>25.99961070681928</v>
       </c>
       <c r="G19" t="n">
-        <v>5.089408528198074</v>
+        <v>5.426455675325304</v>
       </c>
       <c r="H19" t="n">
-        <v>30.12379642365887</v>
+        <v>30.20845852934514</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>19.66987620357634</v>
+        <v>20.30580809647322</v>
       </c>
     </row>
     <row r="20">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.04961020552799</v>
+        <v>29.66533028905089</v>
       </c>
       <c r="E20" t="n">
-        <v>28.63217576187101</v>
+        <v>28.64056786520546</v>
       </c>
       <c r="F20" t="n">
-        <v>13.81998582565556</v>
+        <v>13.95557571270841</v>
       </c>
       <c r="G20" t="n">
-        <v>13.81998582565556</v>
+        <v>13.41021850089568</v>
       </c>
       <c r="H20" t="n">
-        <v>6.66194188518781</v>
+        <v>7.190515382897162</v>
       </c>
       <c r="I20" t="n">
-        <v>7.016300496102056</v>
+        <v>7.13779224924241</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1167,25 +1167,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.791505791505791</v>
+        <v>5.962885580973474</v>
       </c>
       <c r="E21" t="n">
-        <v>13.77091377091377</v>
+        <v>13.26189209326267</v>
       </c>
       <c r="F21" t="n">
-        <v>26.64092664092664</v>
+        <v>25.81344464569478</v>
       </c>
       <c r="G21" t="n">
-        <v>4.761904761904762</v>
+        <v>5.058781020956552</v>
       </c>
       <c r="H21" t="n">
-        <v>29.47232947232947</v>
+        <v>29.85880207323746</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>19.56241956241956</v>
+        <v>20.04419458587508</v>
       </c>
     </row>
     <row r="22">
@@ -1203,22 +1203,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28.29036635006784</v>
+        <v>28.01375026006664</v>
       </c>
       <c r="E22" t="n">
-        <v>27.54409769335143</v>
+        <v>27.95819212323221</v>
       </c>
       <c r="F22" t="n">
-        <v>14.51831750339213</v>
+        <v>14.41525876691877</v>
       </c>
       <c r="G22" t="n">
-        <v>15.26458616010855</v>
+        <v>14.60832204647344</v>
       </c>
       <c r="H22" t="n">
-        <v>7.598371777476255</v>
+        <v>8.027801169123791</v>
       </c>
       <c r="I22" t="n">
-        <v>6.784260515603799</v>
+        <v>6.976675634185142</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1239,25 +1239,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8.880778588807786</v>
+        <v>8.418514812012845</v>
       </c>
       <c r="E23" t="n">
-        <v>11.0705596107056</v>
+        <v>11.04428999182015</v>
       </c>
       <c r="F23" t="n">
-        <v>30.5352798053528</v>
+        <v>29.20655095008543</v>
       </c>
       <c r="G23" t="n">
-        <v>4.744525547445255</v>
+        <v>5.131978082455554</v>
       </c>
       <c r="H23" t="n">
-        <v>28.1021897810219</v>
+        <v>28.39383879218376</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>16.66666666666666</v>
+        <v>17.80482737144225</v>
       </c>
     </row>
     <row r="24">
@@ -1275,22 +1275,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>25.78077158603796</v>
+        <v>26.05483088933808</v>
       </c>
       <c r="E24" t="n">
-        <v>31.78199632578077</v>
+        <v>31.4644404295199</v>
       </c>
       <c r="F24" t="n">
-        <v>15.98285364360073</v>
+        <v>15.5713356043062</v>
       </c>
       <c r="G24" t="n">
-        <v>10.16533986527863</v>
+        <v>10.37230477790869</v>
       </c>
       <c r="H24" t="n">
-        <v>8.266993263931415</v>
+        <v>8.706579883331296</v>
       </c>
       <c r="I24" t="n">
-        <v>8.022045315370484</v>
+        <v>7.830508415595829</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1311,25 +1311,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.6353591160221</v>
+        <v>5.817795331269553</v>
       </c>
       <c r="E25" t="n">
-        <v>14.14364640883978</v>
+        <v>13.45236783708893</v>
       </c>
       <c r="F25" t="n">
-        <v>21.65745856353591</v>
+        <v>21.7327923632143</v>
       </c>
       <c r="G25" t="n">
-        <v>4.198895027624309</v>
+        <v>4.708978937137847</v>
       </c>
       <c r="H25" t="n">
-        <v>34.14364640883978</v>
+        <v>33.58112187658667</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>20.22099447513812</v>
+        <v>20.70694365470271</v>
       </c>
     </row>
     <row r="26">
@@ -1347,22 +1347,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.49681897050318</v>
+        <v>29.03108075089226</v>
       </c>
       <c r="E26" t="n">
-        <v>31.00057836899942</v>
+        <v>30.85962059308143</v>
       </c>
       <c r="F26" t="n">
-        <v>13.0133024869867</v>
+        <v>13.1549411198136</v>
       </c>
       <c r="G26" t="n">
-        <v>11.39386928860613</v>
+        <v>11.36633871509094</v>
       </c>
       <c r="H26" t="n">
-        <v>8.906882591093117</v>
+        <v>9.165916874664811</v>
       </c>
       <c r="I26" t="n">
-        <v>6.188548293811452</v>
+        <v>6.422101946456962</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1383,25 +1383,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5.555555555555555</v>
+        <v>5.694817257256546</v>
       </c>
       <c r="E27" t="n">
-        <v>12.71604938271605</v>
+        <v>12.3974837560121</v>
       </c>
       <c r="F27" t="n">
-        <v>27.16049382716049</v>
+        <v>26.42138227290529</v>
       </c>
       <c r="G27" t="n">
-        <v>4.197530864197531</v>
+        <v>4.683563857195549</v>
       </c>
       <c r="H27" t="n">
-        <v>28.14814814814815</v>
+        <v>28.64280955835951</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>22.22222222222222</v>
+        <v>22.15994329827101</v>
       </c>
     </row>
     <row r="28">
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24.7624371157071</v>
+        <v>25.23880813996855</v>
       </c>
       <c r="E28" t="n">
-        <v>33.14700950251537</v>
+        <v>32.40864393229423</v>
       </c>
       <c r="F28" t="n">
-        <v>16.37786472889882</v>
+        <v>16.08507324189247</v>
       </c>
       <c r="G28" t="n">
-        <v>12.80044717719396</v>
+        <v>12.58327991439264</v>
       </c>
       <c r="H28" t="n">
-        <v>7.490217998882057</v>
+        <v>7.905384820166739</v>
       </c>
       <c r="I28" t="n">
-        <v>5.422023476802683</v>
+        <v>5.778809951285364</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1455,25 +1455,25 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7.77903043968433</v>
+        <v>7.545039236079008</v>
       </c>
       <c r="E29" t="n">
-        <v>9.582863585118377</v>
+        <v>9.80325110258528</v>
       </c>
       <c r="F29" t="n">
-        <v>24.80270574971815</v>
+        <v>24.38028259144554</v>
       </c>
       <c r="G29" t="n">
-        <v>4.96054114994363</v>
+        <v>5.247547198020765</v>
       </c>
       <c r="H29" t="n">
-        <v>31.90529875986471</v>
+        <v>31.87970017477642</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>20.9695603156708</v>
+        <v>21.14417969709298</v>
       </c>
     </row>
     <row r="30">
@@ -1491,22 +1491,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27.84741144414169</v>
+        <v>27.77624596582426</v>
       </c>
       <c r="E30" t="n">
-        <v>31.33514986376022</v>
+        <v>30.96734973991948</v>
       </c>
       <c r="F30" t="n">
-        <v>12.75204359673024</v>
+        <v>13.00385742189678</v>
       </c>
       <c r="G30" t="n">
-        <v>12.9700272479564</v>
+        <v>12.67241113007315</v>
       </c>
       <c r="H30" t="n">
-        <v>8.446866485013624</v>
+        <v>8.740986874713174</v>
       </c>
       <c r="I30" t="n">
-        <v>6.64850136239782</v>
+        <v>6.839148867573165</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1527,25 +1527,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.360157016683022</v>
+        <v>7.207473448233424</v>
       </c>
       <c r="E31" t="n">
-        <v>11.67811579980373</v>
+        <v>11.57267290235317</v>
       </c>
       <c r="F31" t="n">
-        <v>23.25809617271835</v>
+        <v>23.22595656852365</v>
       </c>
       <c r="G31" t="n">
-        <v>6.771344455348381</v>
+        <v>6.772153526741818</v>
       </c>
       <c r="H31" t="n">
-        <v>33.26790971540726</v>
+        <v>32.66370664455876</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>17.66437684003925</v>
+        <v>18.55803690958916</v>
       </c>
     </row>
     <row r="32">
@@ -1563,22 +1563,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20.801317233809</v>
+        <v>21.93909384023159</v>
       </c>
       <c r="E32" t="n">
-        <v>31.55872667398463</v>
+        <v>31.1708896245028</v>
       </c>
       <c r="F32" t="n">
-        <v>18.11196487376509</v>
+        <v>17.45878798707485</v>
       </c>
       <c r="G32" t="n">
-        <v>12.07464324917673</v>
+        <v>11.94991558100211</v>
       </c>
       <c r="H32" t="n">
-        <v>10.53787047200878</v>
+        <v>10.45970142510114</v>
       </c>
       <c r="I32" t="n">
-        <v>6.915477497255764</v>
+        <v>7.021611542087521</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1599,25 +1599,25 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.580558055805581</v>
+        <v>5.688679302041034</v>
       </c>
       <c r="E33" t="n">
-        <v>12.06120612061206</v>
+        <v>11.74573671600232</v>
       </c>
       <c r="F33" t="n">
-        <v>24.57245724572457</v>
+        <v>24.34470203703114</v>
       </c>
       <c r="G33" t="n">
-        <v>5.940594059405941</v>
+        <v>6.102626668251715</v>
       </c>
       <c r="H33" t="n">
-        <v>28.71287128712871</v>
+        <v>29.03987869127555</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>23.13231323132313</v>
+        <v>23.07837658539824</v>
       </c>
     </row>
     <row r="34">
@@ -1635,22 +1635,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.1670146137787</v>
+        <v>29.24792214740007</v>
       </c>
       <c r="E34" t="n">
-        <v>28.18371607515658</v>
+        <v>28.735262163287</v>
       </c>
       <c r="F34" t="n">
-        <v>13.15240083507307</v>
+        <v>13.82777938204736</v>
       </c>
       <c r="G34" t="n">
-        <v>13.04801670146138</v>
+        <v>12.76114110140308</v>
       </c>
       <c r="H34" t="n">
-        <v>7.306889352818372</v>
+        <v>7.472606756133736</v>
       </c>
       <c r="I34" t="n">
-        <v>8.1419624217119</v>
+        <v>7.955288449728766</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -1671,25 +1671,25 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7.116104868913857</v>
+        <v>7.511750762508494</v>
       </c>
       <c r="E35" t="n">
-        <v>10.1123595505618</v>
+        <v>10.57028625057674</v>
       </c>
       <c r="F35" t="n">
-        <v>25.84269662921348</v>
+        <v>26.35924081509527</v>
       </c>
       <c r="G35" t="n">
-        <v>5.149812734082397</v>
+        <v>5.009808475826199</v>
       </c>
       <c r="H35" t="n">
-        <v>33.98876404494382</v>
+        <v>32.85722130083674</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>17.79026217228464</v>
+        <v>17.69169239515654</v>
       </c>
     </row>
     <row r="36">
@@ -1707,22 +1707,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>24.17582417582418</v>
+        <v>24.48615062157985</v>
       </c>
       <c r="E36" t="n">
-        <v>29.71810797897754</v>
+        <v>30.06876435318244</v>
       </c>
       <c r="F36" t="n">
-        <v>17.58241758241758</v>
+        <v>17.30219620355922</v>
       </c>
       <c r="G36" t="n">
-        <v>12.23124701385571</v>
+        <v>12.05822753211691</v>
       </c>
       <c r="H36" t="n">
-        <v>8.743430482560917</v>
+        <v>8.721619451763182</v>
       </c>
       <c r="I36" t="n">
-        <v>7.54897276636407</v>
+        <v>7.36304183779841</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.590509666080843</v>
+        <v>7.040637893596147</v>
       </c>
       <c r="E37" t="n">
-        <v>12.12653778558875</v>
+        <v>12.24912458722863</v>
       </c>
       <c r="F37" t="n">
-        <v>26.36203866432337</v>
+        <v>26.78968954864129</v>
       </c>
       <c r="G37" t="n">
-        <v>4.393673110720562</v>
+        <v>4.337743236018015</v>
       </c>
       <c r="H37" t="n">
-        <v>30.49209138840071</v>
+        <v>30.10702642542104</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>20.03514938488576</v>
+        <v>19.47577830909487</v>
       </c>
     </row>
     <row r="38">
@@ -1779,22 +1779,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>25.80340264650284</v>
+        <v>25.74655179683877</v>
       </c>
       <c r="E38" t="n">
-        <v>30.4820415879017</v>
+        <v>30.84552401207588</v>
       </c>
       <c r="F38" t="n">
-        <v>17.76937618147448</v>
+        <v>17.42334400080148</v>
       </c>
       <c r="G38" t="n">
-        <v>11.3421550094518</v>
+        <v>11.28096244607793</v>
       </c>
       <c r="H38" t="n">
-        <v>7.088846880907372</v>
+        <v>7.369920062297185</v>
       </c>
       <c r="I38" t="n">
-        <v>7.514177693761814</v>
+        <v>7.333697681908758</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -1815,25 +1815,25 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.565987599645705</v>
+        <v>9.456283848575492</v>
       </c>
       <c r="E39" t="n">
-        <v>8.591674047829938</v>
+        <v>9.299645530054457</v>
       </c>
       <c r="F39" t="n">
-        <v>24.62356067316209</v>
+        <v>25.33067388859862</v>
       </c>
       <c r="G39" t="n">
-        <v>3.985828166519043</v>
+        <v>3.974024596375399</v>
       </c>
       <c r="H39" t="n">
-        <v>30.29229406554473</v>
+        <v>30.09832104955876</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>22.94065544729849</v>
+        <v>21.84105108683728</v>
       </c>
     </row>
     <row r="40">
@@ -1851,22 +1851,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>30.18037835459745</v>
+        <v>29.29437473433717</v>
       </c>
       <c r="E40" t="n">
-        <v>28.2446106467224</v>
+        <v>28.77019955467173</v>
       </c>
       <c r="F40" t="n">
-        <v>12.89045314562252</v>
+        <v>13.53837808579775</v>
       </c>
       <c r="G40" t="n">
-        <v>12.97844258688957</v>
+        <v>12.78821817326357</v>
       </c>
       <c r="H40" t="n">
-        <v>9.50285965684118</v>
+        <v>9.321683032063028</v>
       </c>
       <c r="I40" t="n">
-        <v>6.203255609326881</v>
+        <v>6.28714641986674</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -1887,25 +1887,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7.108239095315025</v>
+        <v>7.42841613180709</v>
       </c>
       <c r="E41" t="n">
-        <v>11.95476575121163</v>
+        <v>11.94230896780103</v>
       </c>
       <c r="F41" t="n">
-        <v>25.68659127625202</v>
+        <v>26.18777528011179</v>
       </c>
       <c r="G41" t="n">
-        <v>4.119547657512116</v>
+        <v>4.122517287902305</v>
       </c>
       <c r="H41" t="n">
-        <v>30.04846526655897</v>
+        <v>29.75835552246415</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>21.08239095315024</v>
+        <v>20.56062680991362</v>
       </c>
     </row>
     <row r="42">
@@ -1923,22 +1923,22 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>23.4641638225256</v>
+        <v>23.7553397129661</v>
       </c>
       <c r="E42" t="n">
-        <v>33.95904436860068</v>
+        <v>33.7316202408743</v>
       </c>
       <c r="F42" t="n">
-        <v>16.46757679180887</v>
+        <v>16.30672752980171</v>
       </c>
       <c r="G42" t="n">
-        <v>10.66552901023891</v>
+        <v>10.75225520996472</v>
       </c>
       <c r="H42" t="n">
-        <v>9.172354948805461</v>
+        <v>9.060857617946704</v>
       </c>
       <c r="I42" t="n">
-        <v>6.271331058020478</v>
+        <v>6.393199688446474</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -1959,25 +1959,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6.158357771260997</v>
+        <v>6.724196939077029</v>
       </c>
       <c r="E43" t="n">
-        <v>12.02346041055718</v>
+        <v>11.9778808112733</v>
       </c>
       <c r="F43" t="n">
-        <v>25.14662756598241</v>
+        <v>25.79705434598364</v>
       </c>
       <c r="G43" t="n">
-        <v>4.472140762463344</v>
+        <v>4.454918109104325</v>
       </c>
       <c r="H43" t="n">
-        <v>32.40469208211144</v>
+        <v>31.63561559140063</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>19.79472140762463</v>
+        <v>19.41033420316108</v>
       </c>
     </row>
     <row r="44">
@@ -1995,22 +1995,22 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>23.28947368421053</v>
+        <v>23.76130065831256</v>
       </c>
       <c r="E44" t="n">
-        <v>33.46491228070175</v>
+        <v>32.94582749218287</v>
       </c>
       <c r="F44" t="n">
-        <v>14.3421052631579</v>
+        <v>14.72746373212554</v>
       </c>
       <c r="G44" t="n">
-        <v>11.31578947368421</v>
+        <v>11.37651014720722</v>
       </c>
       <c r="H44" t="n">
-        <v>10.43859649122807</v>
+        <v>10.07210273917381</v>
       </c>
       <c r="I44" t="n">
-        <v>7.149122807017544</v>
+        <v>7.116795230998016</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2031,25 +2031,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>7.342922028766086</v>
+        <v>7.620540129528928</v>
       </c>
       <c r="E45" t="n">
-        <v>13.17183951551855</v>
+        <v>13.14023510066525</v>
       </c>
       <c r="F45" t="n">
-        <v>25.81377744133232</v>
+        <v>26.12072124849605</v>
       </c>
       <c r="G45" t="n">
-        <v>4.920514761544284</v>
+        <v>4.764270393557643</v>
       </c>
       <c r="H45" t="n">
-        <v>31.03709311127933</v>
+        <v>30.88793973363402</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>17.71385314155943</v>
+        <v>17.46629339411811</v>
       </c>
     </row>
     <row r="46">
@@ -2067,22 +2067,22 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>26.32696390658174</v>
+        <v>26.0725207251306</v>
       </c>
       <c r="E46" t="n">
-        <v>28.76857749469214</v>
+        <v>29.44067543141867</v>
       </c>
       <c r="F46" t="n">
-        <v>17.33899504600141</v>
+        <v>17.12151399223777</v>
       </c>
       <c r="G46" t="n">
-        <v>11.8895966029724</v>
+        <v>11.76607625695032</v>
       </c>
       <c r="H46" t="n">
-        <v>8.987968860580326</v>
+        <v>8.876312226487295</v>
       </c>
       <c r="I46" t="n">
-        <v>6.687898089171974</v>
+        <v>6.722901367775348</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2103,25 +2103,25 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.843853820598006</v>
+        <v>7.265155645613437</v>
       </c>
       <c r="E47" t="n">
-        <v>12.35880398671096</v>
+        <v>12.37813439581004</v>
       </c>
       <c r="F47" t="n">
-        <v>25.98006644518273</v>
+        <v>26.1957956765496</v>
       </c>
       <c r="G47" t="n">
-        <v>3.45514950166113</v>
+        <v>3.615576067187077</v>
       </c>
       <c r="H47" t="n">
-        <v>33.35548172757475</v>
+        <v>32.6174840533642</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>18.00664451827242</v>
+        <v>17.92785416147564</v>
       </c>
     </row>
     <row r="48">
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>25.58834516249533</v>
+        <v>25.74584321939366</v>
       </c>
       <c r="E48" t="n">
-        <v>31.11692192753082</v>
+        <v>31.25352890870926</v>
       </c>
       <c r="F48" t="n">
-        <v>16.80986178558087</v>
+        <v>16.46879747144757</v>
       </c>
       <c r="G48" t="n">
-        <v>11.80425849831901</v>
+        <v>11.83284956013671</v>
       </c>
       <c r="H48" t="n">
-        <v>7.769891669779604</v>
+        <v>7.905457269472915</v>
       </c>
       <c r="I48" t="n">
-        <v>6.91072095629436</v>
+        <v>6.793523570839902</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>8.185840707964601</v>
+        <v>8.334059493347763</v>
       </c>
       <c r="E49" t="n">
-        <v>12.24188790560472</v>
+        <v>12.28660799468395</v>
       </c>
       <c r="F49" t="n">
-        <v>26.10619469026549</v>
+        <v>26.4130110028399</v>
       </c>
       <c r="G49" t="n">
-        <v>4.646017699115045</v>
+        <v>4.543237531032636</v>
       </c>
       <c r="H49" t="n">
-        <v>29.35103244837758</v>
+        <v>29.44646035498012</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>19.46902654867257</v>
+        <v>18.97662362311564</v>
       </c>
     </row>
     <row r="50">
@@ -2211,22 +2211,22 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>22.08053691275168</v>
+        <v>22.96458125248807</v>
       </c>
       <c r="E50" t="n">
-        <v>33.05369127516779</v>
+        <v>33.0064511893456</v>
       </c>
       <c r="F50" t="n">
-        <v>16.91275167785235</v>
+        <v>16.26487501605112</v>
       </c>
       <c r="G50" t="n">
-        <v>12.01342281879195</v>
+        <v>11.877874854955</v>
       </c>
       <c r="H50" t="n">
-        <v>8.25503355704698</v>
+        <v>8.025601627515211</v>
       </c>
       <c r="I50" t="n">
-        <v>7.684563758389262</v>
+        <v>7.860616059645001</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2247,25 +2247,25 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7.475994513031551</v>
+        <v>7.51167387722345</v>
       </c>
       <c r="E51" t="n">
-        <v>12.20850480109739</v>
+        <v>12.47149877422269</v>
       </c>
       <c r="F51" t="n">
-        <v>22.08504801097394</v>
+        <v>22.55393762918626</v>
       </c>
       <c r="G51" t="n">
-        <v>4.252400548696845</v>
+        <v>4.173177588765472</v>
       </c>
       <c r="H51" t="n">
-        <v>33.05898491083676</v>
+        <v>32.46618739165984</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>20.91906721536351</v>
+        <v>20.8235247389423</v>
       </c>
     </row>
     <row r="52">
@@ -2283,22 +2283,22 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>28.27542237806821</v>
+        <v>28.18710137668898</v>
       </c>
       <c r="E52" t="n">
-        <v>32.16448836467963</v>
+        <v>32.35127352382367</v>
       </c>
       <c r="F52" t="n">
-        <v>12.94230156200191</v>
+        <v>12.98342900656751</v>
       </c>
       <c r="G52" t="n">
-        <v>12.75103602167676</v>
+        <v>12.52781489008049</v>
       </c>
       <c r="H52" t="n">
-        <v>8.256295824035703</v>
+        <v>7.971409213051873</v>
       </c>
       <c r="I52" t="n">
-        <v>5.610455849537775</v>
+        <v>5.978971989787472</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2319,25 +2319,25 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.809229037703996</v>
+        <v>6.921372309931617</v>
       </c>
       <c r="E53" t="n">
-        <v>14.18120427687113</v>
+        <v>14.1024903911067</v>
       </c>
       <c r="F53" t="n">
-        <v>28.13731007315701</v>
+        <v>27.65032916864924</v>
       </c>
       <c r="G53" t="n">
-        <v>4.220596510973551</v>
+        <v>4.168781109848096</v>
       </c>
       <c r="H53" t="n">
-        <v>31.28868880135059</v>
+        <v>31.03955729650233</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>15.36297129994372</v>
+        <v>16.11746972396202</v>
       </c>
     </row>
     <row r="54">
@@ -2355,22 +2355,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>24.76220672162334</v>
+        <v>25.23005494637803</v>
       </c>
       <c r="E54" t="n">
-        <v>32.05453392517438</v>
+        <v>32.08344824082453</v>
       </c>
       <c r="F54" t="n">
-        <v>15.63094483195942</v>
+        <v>15.34321263292535</v>
       </c>
       <c r="G54" t="n">
-        <v>13.34812935954344</v>
+        <v>13.05246876636964</v>
       </c>
       <c r="H54" t="n">
-        <v>8.275206087507927</v>
+        <v>8.046341610937926</v>
       </c>
       <c r="I54" t="n">
-        <v>5.928979074191503</v>
+        <v>6.244473802564526</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -2391,25 +2391,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7.505399568034557</v>
+        <v>7.654790973547103</v>
       </c>
       <c r="E55" t="n">
-        <v>14.2548596112311</v>
+        <v>14.31879716882417</v>
       </c>
       <c r="F55" t="n">
-        <v>27.64578833693305</v>
+        <v>26.93950840052714</v>
       </c>
       <c r="G55" t="n">
-        <v>4.58963282937365</v>
+        <v>4.461672146131613</v>
       </c>
       <c r="H55" t="n">
-        <v>29.04967602591793</v>
+        <v>29.29455482102013</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>16.95464362850972</v>
+        <v>17.33067648994985</v>
       </c>
     </row>
     <row r="56">
@@ -2427,22 +2427,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>29.56570155902005</v>
+        <v>29.36499960707946</v>
       </c>
       <c r="E56" t="n">
-        <v>31.87639198218263</v>
+        <v>31.89846020535384</v>
       </c>
       <c r="F56" t="n">
-        <v>12.22160356347439</v>
+        <v>12.39092696333825</v>
       </c>
       <c r="G56" t="n">
-        <v>11.33073496659243</v>
+        <v>11.36502008725042</v>
       </c>
       <c r="H56" t="n">
-        <v>8.296213808463252</v>
+        <v>8.036528055018524</v>
       </c>
       <c r="I56" t="n">
-        <v>6.70935412026726</v>
+        <v>6.9440650819595</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -2463,25 +2463,25 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6.44316396018858</v>
+        <v>6.596609224806871</v>
       </c>
       <c r="E57" t="n">
-        <v>12.41487689889995</v>
+        <v>12.62569002567695</v>
       </c>
       <c r="F57" t="n">
-        <v>24.41068622315348</v>
+        <v>24.43974204324991</v>
       </c>
       <c r="G57" t="n">
-        <v>4.714510214772132</v>
+        <v>4.573968364957049</v>
       </c>
       <c r="H57" t="n">
-        <v>30.06809848088004</v>
+        <v>30.27444605144179</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>21.94866422210582</v>
+        <v>21.48954428986744</v>
       </c>
     </row>
     <row r="58">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>28.17976257772753</v>
+        <v>28.16167424038592</v>
       </c>
       <c r="E58" t="n">
-        <v>29.36687394007914</v>
+        <v>29.60615920921535</v>
       </c>
       <c r="F58" t="n">
-        <v>16.59129451667609</v>
+        <v>16.08600548124931</v>
       </c>
       <c r="G58" t="n">
-        <v>12.29508196721311</v>
+        <v>12.25886412756991</v>
       </c>
       <c r="H58" t="n">
-        <v>6.07687959299039</v>
+        <v>6.234756744048351</v>
       </c>
       <c r="I58" t="n">
-        <v>7.490107405313736</v>
+        <v>7.652540197531168</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2535,25 +2535,25 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5.61072492552135</v>
+        <v>5.92995520775358</v>
       </c>
       <c r="E59" t="n">
-        <v>9.582919563058589</v>
+        <v>10.23240272205174</v>
       </c>
       <c r="F59" t="n">
-        <v>29.44389275074479</v>
+        <v>28.56304957310199</v>
       </c>
       <c r="G59" t="n">
-        <v>3.624627606752731</v>
+        <v>3.665094985372218</v>
       </c>
       <c r="H59" t="n">
-        <v>33.6643495531281</v>
+        <v>33.20390160707523</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>18.07348560079444</v>
+        <v>18.40559590464522</v>
       </c>
     </row>
     <row r="60">
@@ -2571,22 +2571,22 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>26.38352638352638</v>
+        <v>26.46995632880916</v>
       </c>
       <c r="E60" t="n">
-        <v>34.51737451737451</v>
+        <v>34.2233619193663</v>
       </c>
       <c r="F60" t="n">
-        <v>13.7966537966538</v>
+        <v>13.73236587899016</v>
       </c>
       <c r="G60" t="n">
-        <v>10.93951093951094</v>
+        <v>11.02707725025757</v>
       </c>
       <c r="H60" t="n">
-        <v>7.49034749034749</v>
+        <v>7.417235257104037</v>
       </c>
       <c r="I60" t="n">
-        <v>6.872586872586872</v>
+        <v>7.130003365472777</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -2607,25 +2607,25 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7.181773155027241</v>
+        <v>7.227523135264409</v>
       </c>
       <c r="E61" t="n">
-        <v>12.43189697870233</v>
+        <v>12.71122308094496</v>
       </c>
       <c r="F61" t="n">
-        <v>27.09262010896483</v>
+        <v>26.74108320412521</v>
       </c>
       <c r="G61" t="n">
-        <v>4.655770183259039</v>
+        <v>4.514994816942314</v>
       </c>
       <c r="H61" t="n">
-        <v>30.46062407132244</v>
+        <v>30.28015898757614</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>18.17731550272412</v>
+        <v>18.52501677514696</v>
       </c>
     </row>
     <row r="62">
@@ -2643,22 +2643,22 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>27.02702702702703</v>
+        <v>27.18486961814394</v>
       </c>
       <c r="E62" t="n">
-        <v>29.3644996347699</v>
+        <v>29.80873634410191</v>
       </c>
       <c r="F62" t="n">
-        <v>14.95008522035549</v>
+        <v>14.66823594374483</v>
       </c>
       <c r="G62" t="n">
-        <v>13.73265157048941</v>
+        <v>13.34583849164597</v>
       </c>
       <c r="H62" t="n">
-        <v>7.937667397126856</v>
+        <v>7.749570499981306</v>
       </c>
       <c r="I62" t="n">
-        <v>6.988069150231313</v>
+        <v>7.242749102382044</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -2679,25 +2679,25 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7.233848953594177</v>
+        <v>7.329529123311586</v>
       </c>
       <c r="E63" t="n">
-        <v>9.827115559599637</v>
+        <v>10.53223551422497</v>
       </c>
       <c r="F63" t="n">
-        <v>26.7515923566879</v>
+        <v>26.64530326772084</v>
       </c>
       <c r="G63" t="n">
-        <v>4.45859872611465</v>
+        <v>4.317666336369273</v>
       </c>
       <c r="H63" t="n">
-        <v>31.80163785259327</v>
+        <v>31.38875655299162</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>19.92720655141037</v>
+        <v>19.78650920538171</v>
       </c>
     </row>
     <row r="64">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>26.08200455580866</v>
+        <v>26.30430561007548</v>
       </c>
       <c r="E64" t="n">
-        <v>31.45785876993166</v>
+        <v>31.75108568460473</v>
       </c>
       <c r="F64" t="n">
-        <v>15.42141230068337</v>
+        <v>15.04666881597275</v>
       </c>
       <c r="G64" t="n">
-        <v>10.97949886104784</v>
+        <v>11.01200419417751</v>
       </c>
       <c r="H64" t="n">
-        <v>8.177676537585421</v>
+        <v>7.973114090417504</v>
       </c>
       <c r="I64" t="n">
-        <v>7.881548974943052</v>
+        <v>7.912821604752025</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6.77433826828174</v>
+        <v>6.921189706785327</v>
       </c>
       <c r="E65" t="n">
-        <v>11.97846567967698</v>
+        <v>12.35839607117011</v>
       </c>
       <c r="F65" t="n">
-        <v>24.9887842081651</v>
+        <v>25.09636873404231</v>
       </c>
       <c r="G65" t="n">
-        <v>5.742485419470614</v>
+        <v>5.425306633135763</v>
       </c>
       <c r="H65" t="n">
-        <v>32.2566173171826</v>
+        <v>31.78224805013711</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>18.25930910722297</v>
+        <v>18.41649080472939</v>
       </c>
     </row>
     <row r="66">
@@ -2787,22 +2787,22 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>27.46913580246914</v>
+        <v>27.8367917085478</v>
       </c>
       <c r="E66" t="n">
-        <v>25.51440329218107</v>
+        <v>26.06112463006602</v>
       </c>
       <c r="F66" t="n">
-        <v>16.8724279835391</v>
+        <v>16.56703839921095</v>
       </c>
       <c r="G66" t="n">
-        <v>12.96296296296296</v>
+        <v>12.86367535700503</v>
       </c>
       <c r="H66" t="n">
-        <v>10.21947873799726</v>
+        <v>9.715227876919261</v>
       </c>
       <c r="I66" t="n">
-        <v>6.96159122085048</v>
+        <v>6.956142028250932</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -2823,25 +2823,25 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7.170542635658915</v>
+        <v>7.31312169820131</v>
       </c>
       <c r="E67" t="n">
-        <v>13.69509043927649</v>
+        <v>13.75687668490123</v>
       </c>
       <c r="F67" t="n">
-        <v>23.90180878552972</v>
+        <v>24.74103617357034</v>
       </c>
       <c r="G67" t="n">
-        <v>6.136950904392765</v>
+        <v>6.037410662088623</v>
       </c>
       <c r="H67" t="n">
-        <v>28.55297157622739</v>
+        <v>28.16232577445643</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>20.54263565891473</v>
+        <v>19.98922900678207</v>
       </c>
     </row>
     <row r="68">
@@ -2859,22 +2859,22 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>24.1222366710013</v>
+        <v>25.0811379931395</v>
       </c>
       <c r="E68" t="n">
-        <v>35.370611183355</v>
+        <v>34.35770662352969</v>
       </c>
       <c r="F68" t="n">
-        <v>13.45903771131339</v>
+        <v>13.80852408652398</v>
       </c>
       <c r="G68" t="n">
-        <v>11.54096228868661</v>
+        <v>11.53552872309925</v>
       </c>
       <c r="H68" t="n">
-        <v>7.542262678803641</v>
+        <v>7.494211913737761</v>
       </c>
       <c r="I68" t="n">
-        <v>7.964889466840051</v>
+        <v>7.72289065996983</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>6.042128603104214</v>
+        <v>6.424468575266358</v>
       </c>
       <c r="E69" t="n">
-        <v>12.47228381374723</v>
+        <v>12.71992747360427</v>
       </c>
       <c r="F69" t="n">
-        <v>27.21729490022173</v>
+        <v>27.5870591173335</v>
       </c>
       <c r="G69" t="n">
-        <v>5.044345898004435</v>
+        <v>5.109691122718196</v>
       </c>
       <c r="H69" t="n">
-        <v>27.38359201773836</v>
+        <v>27.22468628868618</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>21.84035476718404</v>
+        <v>20.9341674223915</v>
       </c>
     </row>
     <row r="70">
@@ -2931,22 +2931,22 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>30.64466849984723</v>
+        <v>30.72434676425349</v>
       </c>
       <c r="E70" t="n">
-        <v>28.04766269477543</v>
+        <v>28.01382821252867</v>
       </c>
       <c r="F70" t="n">
-        <v>13.80996028108769</v>
+        <v>14.03881890114106</v>
       </c>
       <c r="G70" t="n">
-        <v>11.94622670333028</v>
+        <v>11.97046613733395</v>
       </c>
       <c r="H70" t="n">
-        <v>8.096547509929728</v>
+        <v>7.940374179443515</v>
       </c>
       <c r="I70" t="n">
-        <v>7.454934311029636</v>
+        <v>7.31216580529932</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -2967,25 +2967,25 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8.759954493742891</v>
+        <v>8.679195663611578</v>
       </c>
       <c r="E71" t="n">
-        <v>10.35267349260523</v>
+        <v>10.9995829884735</v>
       </c>
       <c r="F71" t="n">
-        <v>24.28896473265074</v>
+        <v>25.10112877767581</v>
       </c>
       <c r="G71" t="n">
-        <v>5.233219567690557</v>
+        <v>5.231205754408896</v>
       </c>
       <c r="H71" t="n">
-        <v>32.08191126279863</v>
+        <v>31.09913533219456</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>19.28327645051194</v>
+        <v>18.88975148363567</v>
       </c>
     </row>
     <row r="72">
@@ -3003,22 +3003,22 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>26.85481524585394</v>
+        <v>27.53553708027003</v>
       </c>
       <c r="E72" t="n">
-        <v>33.37212685481525</v>
+        <v>32.68172767314493</v>
       </c>
       <c r="F72" t="n">
-        <v>15.39132964794879</v>
+        <v>15.25589324253325</v>
       </c>
       <c r="G72" t="n">
-        <v>9.543206284550481</v>
+        <v>9.837306470954076</v>
       </c>
       <c r="H72" t="n">
-        <v>8.08844922897876</v>
+        <v>7.926871688431045</v>
       </c>
       <c r="I72" t="n">
-        <v>6.750072737852779</v>
+        <v>6.762663844666679</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3039,25 +3039,25 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>7.399898631525595</v>
+        <v>7.559103649175865</v>
       </c>
       <c r="E73" t="n">
-        <v>11.80942726811961</v>
+        <v>12.19259460356723</v>
       </c>
       <c r="F73" t="n">
-        <v>28.58590978205778</v>
+        <v>28.5775228387817</v>
       </c>
       <c r="G73" t="n">
-        <v>4.561581348200709</v>
+        <v>4.685249779593465</v>
       </c>
       <c r="H73" t="n">
-        <v>26.71059300557527</v>
+        <v>26.70654642919414</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>20.93258996452104</v>
+        <v>20.2789826996876</v>
       </c>
     </row>
     <row r="74">
@@ -3075,22 +3075,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.31625183016105</v>
+        <v>28.66695208387502</v>
       </c>
       <c r="E74" t="n">
-        <v>29.72181551976574</v>
+        <v>29.45783432567695</v>
       </c>
       <c r="F74" t="n">
-        <v>13.87994143484627</v>
+        <v>14.12633455548725</v>
       </c>
       <c r="G74" t="n">
-        <v>11.53733528550513</v>
+        <v>11.66229483706618</v>
       </c>
       <c r="H74" t="n">
-        <v>9.604685212298682</v>
+        <v>9.199052588249048</v>
       </c>
       <c r="I74" t="n">
-        <v>6.939970717423133</v>
+        <v>6.887531609645553</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -3111,25 +3111,25 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7.454445057979017</v>
+        <v>7.546138019342465</v>
       </c>
       <c r="E75" t="n">
-        <v>13.69409166206516</v>
+        <v>13.71120540652527</v>
       </c>
       <c r="F75" t="n">
-        <v>24.62727774710105</v>
+        <v>25.3321112742421</v>
       </c>
       <c r="G75" t="n">
-        <v>6.129210381004969</v>
+        <v>6.028198665785861</v>
       </c>
       <c r="H75" t="n">
-        <v>29.92821645499724</v>
+        <v>29.34161691854558</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>18.16675869685257</v>
+        <v>18.04072971555872</v>
       </c>
     </row>
     <row r="76">
@@ -3147,22 +3147,22 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27.1536523929471</v>
+        <v>27.88960974910097</v>
       </c>
       <c r="E76" t="n">
-        <v>30.70528967254408</v>
+        <v>30.19115927975941</v>
       </c>
       <c r="F76" t="n">
-        <v>17.45591939546599</v>
+        <v>17.07467326092385</v>
       </c>
       <c r="G76" t="n">
-        <v>12.59445843828715</v>
+        <v>12.52553383383626</v>
       </c>
       <c r="H76" t="n">
-        <v>5.188916876574307</v>
+        <v>5.474901086338599</v>
       </c>
       <c r="I76" t="n">
-        <v>6.90176322418136</v>
+        <v>6.844122790040916</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>7.53667172483561</v>
+        <v>7.59062074734356</v>
       </c>
       <c r="E77" t="n">
-        <v>11.22913505311077</v>
+        <v>11.67836905908117</v>
       </c>
       <c r="F77" t="n">
-        <v>31.05715730905412</v>
+        <v>30.66628162654169</v>
       </c>
       <c r="G77" t="n">
-        <v>4.400606980273141</v>
+        <v>4.542938170327005</v>
       </c>
       <c r="H77" t="n">
-        <v>30.65250379362671</v>
+        <v>30.04903387261733</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>15.12392513909965</v>
+        <v>15.47275652408925</v>
       </c>
     </row>
     <row r="78">
@@ -3219,22 +3219,22 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>24.93143170597915</v>
+        <v>25.97347282926252</v>
       </c>
       <c r="E78" t="n">
-        <v>28.66154690071311</v>
+        <v>28.42172529344503</v>
       </c>
       <c r="F78" t="n">
-        <v>16.59352715304443</v>
+        <v>16.42637210688291</v>
       </c>
       <c r="G78" t="n">
-        <v>14.23477783872737</v>
+        <v>13.9500247511448</v>
       </c>
       <c r="H78" t="n">
-        <v>7.953922106417992</v>
+        <v>7.779452240869582</v>
       </c>
       <c r="I78" t="n">
-        <v>7.624794295117937</v>
+        <v>7.448952778395161</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -3255,25 +3255,25 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>7.848568790397045</v>
+        <v>7.936766845455582</v>
       </c>
       <c r="E79" t="n">
-        <v>12.00369344413666</v>
+        <v>12.43199444806189</v>
       </c>
       <c r="F79" t="n">
-        <v>32.54847645429363</v>
+        <v>31.9091118479553</v>
       </c>
       <c r="G79" t="n">
-        <v>3.231763619575254</v>
+        <v>3.591812044369822</v>
       </c>
       <c r="H79" t="n">
-        <v>30.60941828254848</v>
+        <v>29.91564820904348</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>13.75807940904894</v>
+        <v>14.21466660511391</v>
       </c>
     </row>
     <row r="80">
@@ -3291,22 +3291,22 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28.9172831203766</v>
+        <v>29.09270004332732</v>
       </c>
       <c r="E80" t="n">
-        <v>32.77292086976014</v>
+        <v>32.11005103569315</v>
       </c>
       <c r="F80" t="n">
-        <v>12.77740416946873</v>
+        <v>13.27964687834844</v>
       </c>
       <c r="G80" t="n">
-        <v>10.28917283120377</v>
+        <v>10.55235721136486</v>
       </c>
       <c r="H80" t="n">
-        <v>7.218112530822686</v>
+        <v>7.190068407689855</v>
       </c>
       <c r="I80" t="n">
-        <v>8.025106478368079</v>
+        <v>7.775176423576381</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -3327,25 +3327,25 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>7.152259763053971</v>
+        <v>7.320983893743869</v>
       </c>
       <c r="E81" t="n">
-        <v>14.12900394910048</v>
+        <v>14.14635744740632</v>
       </c>
       <c r="F81" t="n">
-        <v>25.66915313734094</v>
+        <v>26.32213051031743</v>
       </c>
       <c r="G81" t="n">
-        <v>3.685827117156647</v>
+        <v>3.978507080704005</v>
       </c>
       <c r="H81" t="n">
-        <v>27.42430890741553</v>
+        <v>27.09054631070085</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>21.93944712593242</v>
+        <v>21.14147475712753</v>
       </c>
     </row>
     <row r="82">
@@ -3363,22 +3363,22 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>24.87100103199174</v>
+        <v>24.65733228795371</v>
       </c>
       <c r="E82" t="n">
-        <v>34.82972136222911</v>
+        <v>33.98930598979204</v>
       </c>
       <c r="F82" t="n">
-        <v>14.86068111455108</v>
+        <v>15.40721988817593</v>
       </c>
       <c r="G82" t="n">
-        <v>11.04231166150671</v>
+        <v>11.13059060035946</v>
       </c>
       <c r="H82" t="n">
-        <v>7.275541795665634</v>
+        <v>7.510556265824266</v>
       </c>
       <c r="I82" t="n">
-        <v>7.120743034055728</v>
+        <v>7.304994967894575</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3399,25 +3399,25 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>7.314524555903866</v>
+        <v>7.069580909264574</v>
       </c>
       <c r="E83" t="n">
-        <v>11.18077324973877</v>
+        <v>11.9006424949239</v>
       </c>
       <c r="F83" t="n">
-        <v>23.30198537095089</v>
+        <v>23.33347433626301</v>
       </c>
       <c r="G83" t="n">
-        <v>4.284221525600835</v>
+        <v>4.333035866707789</v>
       </c>
       <c r="H83" t="n">
-        <v>33.5423197492163</v>
+        <v>32.94965835134287</v>
       </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>20.37617554858934</v>
+        <v>20.41360804149787</v>
       </c>
     </row>
     <row r="84">
@@ -3435,22 +3435,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>28.87975334018499</v>
+        <v>27.66148066376943</v>
       </c>
       <c r="E84" t="n">
-        <v>27.85200411099692</v>
+        <v>28.48591179544315</v>
       </c>
       <c r="F84" t="n">
-        <v>16.54676258992806</v>
+        <v>16.76459078620027</v>
       </c>
       <c r="G84" t="n">
-        <v>11.76772867420349</v>
+        <v>11.74416763075504</v>
       </c>
       <c r="H84" t="n">
-        <v>8.478931140801645</v>
+        <v>8.505768131687246</v>
       </c>
       <c r="I84" t="n">
-        <v>6.474820143884892</v>
+        <v>6.83808099214487</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -3471,25 +3471,25 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>6.309420916162489</v>
+        <v>6.215899264824416</v>
       </c>
       <c r="E85" t="n">
-        <v>11.92739844425238</v>
+        <v>12.64236812564293</v>
       </c>
       <c r="F85" t="n">
-        <v>28.17631806395851</v>
+        <v>27.23473655291929</v>
       </c>
       <c r="G85" t="n">
-        <v>5.617977528089887</v>
+        <v>5.404108097695443</v>
       </c>
       <c r="H85" t="n">
-        <v>29.81849611063094</v>
+        <v>29.96313674210067</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>18.15038893690579</v>
+        <v>18.53975121681726</v>
       </c>
     </row>
     <row r="86">
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>28.1751192024274</v>
+        <v>27.35535391529044</v>
       </c>
       <c r="E86" t="n">
-        <v>27.91504117902037</v>
+        <v>28.16957826653543</v>
       </c>
       <c r="F86" t="n">
-        <v>17.94538361508453</v>
+        <v>17.94119843322205</v>
       </c>
       <c r="G86" t="n">
-        <v>12.65713047247507</v>
+        <v>12.60824998633121</v>
       </c>
       <c r="H86" t="n">
-        <v>7.542262678803641</v>
+        <v>7.679159310866754</v>
       </c>
       <c r="I86" t="n">
-        <v>5.76506285218899</v>
+        <v>6.246460087754122</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -3543,25 +3543,25 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>8.016877637130802</v>
+        <v>7.625804916254117</v>
       </c>
       <c r="E87" t="n">
-        <v>11.47679324894515</v>
+        <v>12.14691329898731</v>
       </c>
       <c r="F87" t="n">
-        <v>29.28270042194093</v>
+        <v>28.15349917604647</v>
       </c>
       <c r="G87" t="n">
-        <v>4.725738396624473</v>
+        <v>4.5785717175762</v>
       </c>
       <c r="H87" t="n">
-        <v>29.62025316455696</v>
+        <v>29.9105937822968</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>16.87763713080169</v>
+        <v>17.5846171088391</v>
       </c>
     </row>
     <row r="88">
@@ -3579,22 +3579,22 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>23.56930902924968</v>
+        <v>23.46739771007108</v>
       </c>
       <c r="E88" t="n">
-        <v>34.97244595167444</v>
+        <v>34.03043747662683</v>
       </c>
       <c r="F88" t="n">
-        <v>14.15854175498092</v>
+        <v>14.90381229935186</v>
       </c>
       <c r="G88" t="n">
-        <v>11.36074607884697</v>
+        <v>11.47570389689978</v>
       </c>
       <c r="H88" t="n">
-        <v>8.902077151335313</v>
+        <v>8.842785718963201</v>
       </c>
       <c r="I88" t="n">
-        <v>7.036880033912675</v>
+        <v>7.279862898087257</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -3615,25 +3615,25 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7.475083056478406</v>
+        <v>7.255746383304536</v>
       </c>
       <c r="E89" t="n">
-        <v>12.95681063122924</v>
+        <v>13.46614402361076</v>
       </c>
       <c r="F89" t="n">
-        <v>29.31893687707641</v>
+        <v>28.19174282174318</v>
       </c>
       <c r="G89" t="n">
-        <v>3.073089700996678</v>
+        <v>3.340566207863679</v>
       </c>
       <c r="H89" t="n">
-        <v>28.57142857142857</v>
+        <v>28.83932968066309</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>18.6046511627907</v>
+        <v>18.90647088281476</v>
       </c>
     </row>
     <row r="90">
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>23.39489885664028</v>
+        <v>23.32291888295307</v>
       </c>
       <c r="E90" t="n">
-        <v>31.97009674582234</v>
+        <v>31.62363512070759</v>
       </c>
       <c r="F90" t="n">
-        <v>15.78715919085312</v>
+        <v>16.07778464013086</v>
       </c>
       <c r="G90" t="n">
-        <v>11.69744942832014</v>
+        <v>11.83437342134379</v>
       </c>
       <c r="H90" t="n">
-        <v>9.938434476693052</v>
+        <v>9.717389596127381</v>
       </c>
       <c r="I90" t="n">
-        <v>7.211961301671065</v>
+        <v>7.423898338737316</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -3687,25 +3687,25 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>7.112970711297072</v>
+        <v>6.894068112293292</v>
       </c>
       <c r="E91" t="n">
-        <v>14.29567642956764</v>
+        <v>14.66330755792787</v>
       </c>
       <c r="F91" t="n">
-        <v>23.91910739191074</v>
+        <v>23.84483760862154</v>
       </c>
       <c r="G91" t="n">
-        <v>4.253835425383542</v>
+        <v>4.255689141156579</v>
       </c>
       <c r="H91" t="n">
-        <v>31.45048814504882</v>
+        <v>31.13708844702422</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>18.96792189679219</v>
+        <v>19.20500913297651</v>
       </c>
     </row>
     <row r="92">
@@ -3723,22 +3723,22 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>26.228107646305</v>
+        <v>25.64508296436151</v>
       </c>
       <c r="E92" t="n">
-        <v>27.68047842802222</v>
+        <v>28.15000684945356</v>
       </c>
       <c r="F92" t="n">
-        <v>17.38573259290902</v>
+        <v>17.48249852220315</v>
       </c>
       <c r="G92" t="n">
-        <v>12.85775309696711</v>
+        <v>12.65896227258229</v>
       </c>
       <c r="H92" t="n">
-        <v>8.073472874839812</v>
+        <v>8.153394728762953</v>
       </c>
       <c r="I92" t="n">
-        <v>7.774455360956855</v>
+        <v>7.910054662636528</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -3759,25 +3759,25 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>6.552494415487714</v>
+        <v>6.500325763066334</v>
       </c>
       <c r="E93" t="n">
-        <v>16.30677587490693</v>
+        <v>16.13710275507622</v>
       </c>
       <c r="F93" t="n">
-        <v>26.58227848101265</v>
+        <v>25.84625267264615</v>
       </c>
       <c r="G93" t="n">
-        <v>4.616530156366344</v>
+        <v>4.633488257026908</v>
       </c>
       <c r="H93" t="n">
-        <v>26.8801191362621</v>
+        <v>27.55761399650169</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>19.06180193596426</v>
+        <v>19.3252165556827</v>
       </c>
     </row>
     <row r="94">
@@ -3795,22 +3795,22 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>27.3109243697479</v>
+        <v>26.58464937163997</v>
       </c>
       <c r="E94" t="n">
-        <v>30.44308632543927</v>
+        <v>30.36687430859633</v>
       </c>
       <c r="F94" t="n">
-        <v>16.34835752482811</v>
+        <v>16.638206710352</v>
       </c>
       <c r="G94" t="n">
-        <v>11.68831168831169</v>
+        <v>11.75397522284102</v>
       </c>
       <c r="H94" t="n">
-        <v>7.448433919022154</v>
+        <v>7.64450662554535</v>
       </c>
       <c r="I94" t="n">
-        <v>6.760886172650879</v>
+        <v>7.011787761025334</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -3831,25 +3831,25 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>5.90851334180432</v>
+        <v>5.943688553564015</v>
       </c>
       <c r="E95" t="n">
-        <v>11.24523506988564</v>
+        <v>12.06173268903218</v>
       </c>
       <c r="F95" t="n">
-        <v>26.55654383735705</v>
+        <v>25.87771932132003</v>
       </c>
       <c r="G95" t="n">
-        <v>5.400254129606099</v>
+        <v>5.170899650574066</v>
       </c>
       <c r="H95" t="n">
-        <v>30.24142312579415</v>
+        <v>30.32207665327357</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>20.64803049555273</v>
+        <v>20.62388313223615</v>
       </c>
     </row>
     <row r="96">
@@ -3867,22 +3867,22 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>28.28070175438597</v>
+        <v>27.3635021915842</v>
       </c>
       <c r="E96" t="n">
-        <v>30.59649122807018</v>
+        <v>30.25143713003476</v>
       </c>
       <c r="F96" t="n">
-        <v>17.08771929824561</v>
+        <v>17.22322416256103</v>
       </c>
       <c r="G96" t="n">
-        <v>10.7719298245614</v>
+        <v>11.1331200387689</v>
       </c>
       <c r="H96" t="n">
-        <v>7.403508771929824</v>
+        <v>7.684502190345841</v>
       </c>
       <c r="I96" t="n">
-        <v>5.859649122807017</v>
+        <v>6.344214286705261</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -3903,25 +3903,25 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>6.73352435530086</v>
+        <v>6.718189097105584</v>
       </c>
       <c r="E97" t="n">
-        <v>12.75071633237822</v>
+        <v>13.34966831178122</v>
       </c>
       <c r="F97" t="n">
-        <v>23.13753581661891</v>
+        <v>23.19436463350334</v>
       </c>
       <c r="G97" t="n">
-        <v>3.223495702005731</v>
+        <v>3.470708871577051</v>
       </c>
       <c r="H97" t="n">
-        <v>32.44985673352436</v>
+        <v>31.84590498235133</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>21.70487106017192</v>
+        <v>21.42116410368148</v>
       </c>
     </row>
     <row r="98">
@@ -3939,22 +3939,22 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>27.80813600485731</v>
+        <v>27.61920008334863</v>
       </c>
       <c r="E98" t="n">
-        <v>32.60473588342441</v>
+        <v>32.11514246339767</v>
       </c>
       <c r="F98" t="n">
-        <v>13.7826350941105</v>
+        <v>14.09318898408606</v>
       </c>
       <c r="G98" t="n">
-        <v>11.35397692774742</v>
+        <v>11.2548601125341</v>
       </c>
       <c r="H98" t="n">
-        <v>8.439587128111718</v>
+        <v>8.562910660861998</v>
       </c>
       <c r="I98" t="n">
-        <v>6.010928961748633</v>
+        <v>6.354697695771545</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -3975,25 +3975,25 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>5.830164765525982</v>
+        <v>6.0796786786163</v>
       </c>
       <c r="E99" t="n">
-        <v>13.30798479087452</v>
+        <v>13.16379102549447</v>
       </c>
       <c r="F99" t="n">
-        <v>27.12294043092523</v>
+        <v>26.619245686693</v>
       </c>
       <c r="G99" t="n">
-        <v>6.337135614702155</v>
+        <v>6.110840670821014</v>
       </c>
       <c r="H99" t="n">
-        <v>26.36248415716096</v>
+        <v>26.66785742604084</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>21.03929024081116</v>
+        <v>21.35858651233439</v>
       </c>
     </row>
     <row r="100">
@@ -4011,22 +4011,22 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>25.77727529677784</v>
+        <v>25.9518773442373</v>
       </c>
       <c r="E100" t="n">
-        <v>32.33465234595817</v>
+        <v>31.83571572378866</v>
       </c>
       <c r="F100" t="n">
-        <v>15.31938948558508</v>
+        <v>15.35464094607304</v>
       </c>
       <c r="G100" t="n">
-        <v>11.41888072357264</v>
+        <v>11.42127405469944</v>
       </c>
       <c r="H100" t="n">
-        <v>8.253250423968343</v>
+        <v>8.330975847838326</v>
       </c>
       <c r="I100" t="n">
-        <v>6.896551724137931</v>
+        <v>7.105516083363225</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -4047,25 +4047,25 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>5.543237250554324</v>
+        <v>5.835153338716858</v>
       </c>
       <c r="E101" t="n">
-        <v>12.19512195121951</v>
+        <v>12.53096418931044</v>
       </c>
       <c r="F101" t="n">
-        <v>25.38802660753881</v>
+        <v>24.77690727481343</v>
       </c>
       <c r="G101" t="n">
-        <v>3.436807095343681</v>
+        <v>3.815801714190782</v>
       </c>
       <c r="H101" t="n">
-        <v>31.1529933481153</v>
+        <v>30.46216719830283</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>22.28381374722838</v>
+        <v>22.57900628466568</v>
       </c>
     </row>
     <row r="102">
@@ -4083,22 +4083,22 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>30.10234798314269</v>
+        <v>29.40551485641217</v>
       </c>
       <c r="E102" t="n">
-        <v>26.42986152919928</v>
+        <v>27.14428366236618</v>
       </c>
       <c r="F102" t="n">
-        <v>14.8103552077062</v>
+        <v>14.98616614389936</v>
       </c>
       <c r="G102" t="n">
-        <v>11.86032510535822</v>
+        <v>11.72225886157274</v>
       </c>
       <c r="H102" t="n">
-        <v>9.030704394942806</v>
+        <v>8.896461769763961</v>
       </c>
       <c r="I102" t="n">
-        <v>7.766405779650813</v>
+        <v>7.845314705985586</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -4119,25 +4119,25 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>7.763975155279502</v>
+        <v>7.567893755680832</v>
       </c>
       <c r="E103" t="n">
-        <v>12.21532091097309</v>
+        <v>12.20579626049697</v>
       </c>
       <c r="F103" t="n">
-        <v>23.39544513457557</v>
+        <v>23.49195044009947</v>
       </c>
       <c r="G103" t="n">
-        <v>5.072463768115942</v>
+        <v>5.055504721130514</v>
       </c>
       <c r="H103" t="n">
-        <v>29.71014492753623</v>
+        <v>29.4766863346231</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>21.84265010351967</v>
+        <v>22.20216848796913</v>
       </c>
     </row>
     <row r="104">
@@ -4155,22 +4155,22 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>24.82014388489209</v>
+        <v>25.13209581802901</v>
       </c>
       <c r="E104" t="n">
-        <v>29.49640287769784</v>
+        <v>29.50838883850679</v>
       </c>
       <c r="F104" t="n">
-        <v>19.01336073997945</v>
+        <v>18.49681971939999</v>
       </c>
       <c r="G104" t="n">
-        <v>11.71634121274409</v>
+        <v>11.64323197754771</v>
       </c>
       <c r="H104" t="n">
-        <v>7.399794450154163</v>
+        <v>7.582495645017723</v>
       </c>
       <c r="I104" t="n">
-        <v>7.553956834532374</v>
+        <v>7.636968001498763</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -4191,25 +4191,25 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>8.785046728971963</v>
+        <v>8.476359700961082</v>
       </c>
       <c r="E105" t="n">
-        <v>12.33644859813084</v>
+        <v>12.54195622016556</v>
       </c>
       <c r="F105" t="n">
-        <v>26.35514018691589</v>
+        <v>25.78055609551847</v>
       </c>
       <c r="G105" t="n">
-        <v>4.766355140186916</v>
+        <v>4.890984784454923</v>
       </c>
       <c r="H105" t="n">
-        <v>27.94392523364486</v>
+        <v>27.82873284161884</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>19.81308411214953</v>
+        <v>20.48141035728113</v>
       </c>
     </row>
     <row r="106">
@@ -4227,22 +4227,22 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>27.705112960761</v>
+        <v>27.43267667478087</v>
       </c>
       <c r="E106" t="n">
-        <v>23.18668252080856</v>
+        <v>24.4281094933755</v>
       </c>
       <c r="F106" t="n">
-        <v>18.19262782401903</v>
+        <v>17.67921087227044</v>
       </c>
       <c r="G106" t="n">
-        <v>13.25802615933413</v>
+        <v>12.90951957523287</v>
       </c>
       <c r="H106" t="n">
-        <v>9.036860879904875</v>
+        <v>8.947548198814195</v>
       </c>
       <c r="I106" t="n">
-        <v>8.620689655172415</v>
+        <v>8.602935185526137</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -4263,25 +4263,25 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>6.653620352250488</v>
+        <v>6.75245198040713</v>
       </c>
       <c r="E107" t="n">
-        <v>13.40508806262231</v>
+        <v>13.30112017671741</v>
       </c>
       <c r="F107" t="n">
-        <v>26.1252446183953</v>
+        <v>25.58261585599044</v>
       </c>
       <c r="G107" t="n">
-        <v>5.47945205479452</v>
+        <v>5.429320304477956</v>
       </c>
       <c r="H107" t="n">
-        <v>29.25636007827789</v>
+        <v>29.08491304969811</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>19.08023483365949</v>
+        <v>19.84957863270897</v>
       </c>
     </row>
     <row r="108">
@@ -4299,22 +4299,22 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>28.95966029723991</v>
+        <v>28.64181049816641</v>
       </c>
       <c r="E108" t="n">
-        <v>29.89384288747346</v>
+        <v>29.76501612321809</v>
       </c>
       <c r="F108" t="n">
-        <v>13.92781316348195</v>
+        <v>14.27220610149822</v>
       </c>
       <c r="G108" t="n">
-        <v>11.59235668789809</v>
+        <v>11.53382940233729</v>
       </c>
       <c r="H108" t="n">
-        <v>8.619957537154988</v>
+        <v>8.640050923168994</v>
       </c>
       <c r="I108" t="n">
-        <v>7.006369426751593</v>
+        <v>7.147086951610987</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -4335,25 +4335,25 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5.963302752293578</v>
+        <v>6.12859816013569</v>
       </c>
       <c r="E109" t="n">
-        <v>13.30275229357798</v>
+        <v>12.99312399217859</v>
       </c>
       <c r="F109" t="n">
-        <v>23.48623853211009</v>
+        <v>23.57171819965441</v>
       </c>
       <c r="G109" t="n">
-        <v>4.128440366972478</v>
+        <v>4.297603205568016</v>
       </c>
       <c r="H109" t="n">
-        <v>32.01834862385321</v>
+        <v>31.4330324583632</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>21.10091743119266</v>
+        <v>21.5759239841001</v>
       </c>
     </row>
     <row r="110">
@@ -4371,22 +4371,22 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>25.39759036144578</v>
+        <v>25.60678292863973</v>
       </c>
       <c r="E110" t="n">
-        <v>29.78313253012048</v>
+        <v>29.78922105490982</v>
       </c>
       <c r="F110" t="n">
-        <v>17.87951807228916</v>
+        <v>17.53809242938306</v>
       </c>
       <c r="G110" t="n">
-        <v>11.27710843373494</v>
+        <v>11.21266511994173</v>
       </c>
       <c r="H110" t="n">
-        <v>7.084337349397591</v>
+        <v>7.330641764123243</v>
       </c>
       <c r="I110" t="n">
-        <v>8.578313253012048</v>
+        <v>8.522596703002408</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -4407,25 +4407,25 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>7.258064516129033</v>
+        <v>7.102545253768939</v>
       </c>
       <c r="E111" t="n">
-        <v>13.44086021505376</v>
+        <v>13.28957727702504</v>
       </c>
       <c r="F111" t="n">
-        <v>26.34408602150538</v>
+        <v>25.96628363097641</v>
       </c>
       <c r="G111" t="n">
-        <v>4.301075268817205</v>
+        <v>4.399129151530279</v>
       </c>
       <c r="H111" t="n">
-        <v>31.54121863799283</v>
+        <v>30.91924048736102</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>17.11469534050179</v>
+        <v>18.32322419933833</v>
       </c>
     </row>
     <row r="112">
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>25.32729103726082</v>
+        <v>25.53914088350379</v>
       </c>
       <c r="E112" t="n">
-        <v>29.50654582074522</v>
+        <v>29.7529907724982</v>
       </c>
       <c r="F112" t="n">
-        <v>14.55186304128902</v>
+        <v>14.66217082847926</v>
       </c>
       <c r="G112" t="n">
-        <v>13.5448136958711</v>
+        <v>13.06534664300375</v>
       </c>
       <c r="H112" t="n">
-        <v>9.566968781470292</v>
+        <v>9.386099654843743</v>
       </c>
       <c r="I112" t="n">
-        <v>7.502517623363544</v>
+        <v>7.594251217671253</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -4479,25 +4479,25 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>7.860615883306322</v>
+        <v>7.585532170736421</v>
       </c>
       <c r="E113" t="n">
-        <v>12.88492706645057</v>
+        <v>12.92427317255525</v>
       </c>
       <c r="F113" t="n">
-        <v>29.74068071312804</v>
+        <v>28.63386921431412</v>
       </c>
       <c r="G113" t="n">
-        <v>4.294975688816856</v>
+        <v>4.420572504196691</v>
       </c>
       <c r="H113" t="n">
-        <v>26.58022690437602</v>
+        <v>26.86387007604375</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>18.6385737439222</v>
+        <v>19.57188286215378</v>
       </c>
     </row>
     <row r="114">
@@ -4515,22 +4515,22 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>28.31505483549352</v>
+        <v>28.51186756444163</v>
       </c>
       <c r="E114" t="n">
-        <v>31.80458624127617</v>
+        <v>31.06602270749071</v>
       </c>
       <c r="F114" t="n">
-        <v>13.26021934197408</v>
+        <v>13.45532429329814</v>
       </c>
       <c r="G114" t="n">
-        <v>14.25722831505484</v>
+        <v>14.16186572956573</v>
       </c>
       <c r="H114" t="n">
-        <v>6.281156530408774</v>
+        <v>6.787607768362151</v>
       </c>
       <c r="I114" t="n">
-        <v>6.081754735792622</v>
+        <v>6.01731193684164</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -4551,25 +4551,25 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>6.2015503875969</v>
+        <v>6.118889331960118</v>
       </c>
       <c r="E115" t="n">
-        <v>9.496124031007753</v>
+        <v>10.00260969874021</v>
       </c>
       <c r="F115" t="n">
-        <v>26.35658914728683</v>
+        <v>27.28568316952727</v>
       </c>
       <c r="G115" t="n">
-        <v>4.651162790697675</v>
+        <v>4.39877771503158</v>
       </c>
       <c r="H115" t="n">
-        <v>32.17054263565892</v>
+        <v>32.25216509134827</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>21.12403100775194</v>
+        <v>19.94187499339256</v>
       </c>
     </row>
     <row r="116">
@@ -4587,22 +4587,22 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>26.90246516613076</v>
+        <v>27.30755628416226</v>
       </c>
       <c r="E116" t="n">
-        <v>30.43944265809218</v>
+        <v>30.08187388574746</v>
       </c>
       <c r="F116" t="n">
-        <v>14.04072883172562</v>
+        <v>14.07192459371052</v>
       </c>
       <c r="G116" t="n">
-        <v>10.61093247588424</v>
+        <v>11.11542720752802</v>
       </c>
       <c r="H116" t="n">
-        <v>8.896034297963558</v>
+        <v>8.843127572602882</v>
       </c>
       <c r="I116" t="n">
-        <v>9.110396570203644</v>
+        <v>8.580090456248866</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -4623,25 +4623,25 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>6.066536203522505</v>
+        <v>6.048935220888414</v>
       </c>
       <c r="E117" t="n">
-        <v>14.48140900195695</v>
+        <v>14.06689147492233</v>
       </c>
       <c r="F117" t="n">
-        <v>33.07240704500978</v>
+        <v>33.17755952505602</v>
       </c>
       <c r="G117" t="n">
-        <v>4.305283757338552</v>
+        <v>3.97867663065331</v>
       </c>
       <c r="H117" t="n">
-        <v>24.65753424657534</v>
+        <v>25.83656548431003</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>17.41682974559687</v>
+        <v>16.89137166416991</v>
       </c>
     </row>
     <row r="118">
@@ -4659,22 +4659,22 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>25.72087658592849</v>
+        <v>26.32532603309049</v>
       </c>
       <c r="E118" t="n">
-        <v>32.64129181084198</v>
+        <v>31.93816224372301</v>
       </c>
       <c r="F118" t="n">
-        <v>16.37831603229527</v>
+        <v>15.99412934151122</v>
       </c>
       <c r="G118" t="n">
-        <v>10.03460207612457</v>
+        <v>10.62603308525449</v>
       </c>
       <c r="H118" t="n">
-        <v>8.304498269896193</v>
+        <v>8.417458088750452</v>
       </c>
       <c r="I118" t="n">
-        <v>6.920415224913495</v>
+        <v>6.69889120767033</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -4695,25 +4695,25 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>6.2</v>
+        <v>6.115980606156808</v>
       </c>
       <c r="E119" t="n">
-        <v>17.2</v>
+        <v>16.17479972722274</v>
       </c>
       <c r="F119" t="n">
-        <v>25.8</v>
+        <v>26.98676338444444</v>
       </c>
       <c r="G119" t="n">
-        <v>5.600000000000001</v>
+        <v>5.224372421376282</v>
       </c>
       <c r="H119" t="n">
-        <v>26.6</v>
+        <v>27.73413261390834</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>18.6</v>
+        <v>17.76395124689137</v>
       </c>
     </row>
     <row r="120">
@@ -4731,22 +4731,22 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>29.625</v>
+        <v>29.53420114330386</v>
       </c>
       <c r="E120" t="n">
-        <v>29.75</v>
+        <v>29.45326595581803</v>
       </c>
       <c r="F120" t="n">
-        <v>14.875</v>
+        <v>14.86704272612716</v>
       </c>
       <c r="G120" t="n">
-        <v>9.375</v>
+        <v>10.11734740001087</v>
       </c>
       <c r="H120" t="n">
-        <v>8</v>
+        <v>8.129100551555117</v>
       </c>
       <c r="I120" t="n">
-        <v>8.375</v>
+        <v>7.899042223184962</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -4767,25 +4767,25 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>9.072164948453608</v>
+        <v>8.376458646483693</v>
       </c>
       <c r="E121" t="n">
-        <v>9.896907216494846</v>
+        <v>10.28318792970206</v>
       </c>
       <c r="F121" t="n">
-        <v>29.89690721649485</v>
+        <v>30.22201763427221</v>
       </c>
       <c r="G121" t="n">
-        <v>3.092783505154639</v>
+        <v>3.236069555658796</v>
       </c>
       <c r="H121" t="n">
-        <v>27.62886597938144</v>
+        <v>28.62916272319499</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>20.41237113402062</v>
+        <v>19.25310351068823</v>
       </c>
     </row>
     <row r="122">
@@ -4803,22 +4803,22 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>27.4390243902439</v>
+        <v>27.84090728056524</v>
       </c>
       <c r="E122" t="n">
-        <v>27.4390243902439</v>
+        <v>27.40991595978124</v>
       </c>
       <c r="F122" t="n">
-        <v>16.21951219512195</v>
+        <v>15.88888427867928</v>
       </c>
       <c r="G122" t="n">
-        <v>13.29268292682927</v>
+        <v>13.34963640763586</v>
       </c>
       <c r="H122" t="n">
-        <v>8.902439024390244</v>
+        <v>8.916081105106572</v>
       </c>
       <c r="I122" t="n">
-        <v>6.707317073170732</v>
+        <v>6.594574968231813</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -4839,25 +4839,25 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>4.357798165137615</v>
+        <v>4.591456343548416</v>
       </c>
       <c r="E123" t="n">
-        <v>11.92660550458716</v>
+        <v>11.91094882474636</v>
       </c>
       <c r="F123" t="n">
-        <v>31.65137614678899</v>
+        <v>31.50544742853433</v>
       </c>
       <c r="G123" t="n">
-        <v>5.73394495412844</v>
+        <v>5.410815843059642</v>
       </c>
       <c r="H123" t="n">
-        <v>27.06422018348624</v>
+        <v>28.19855145211288</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>19.26605504587156</v>
+        <v>18.38278010799837</v>
       </c>
     </row>
     <row r="124">
@@ -4875,22 +4875,22 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>25.20612485276796</v>
+        <v>25.90441821417981</v>
       </c>
       <c r="E124" t="n">
-        <v>31.68433451118963</v>
+        <v>31.14375092051734</v>
       </c>
       <c r="F124" t="n">
-        <v>13.66313309776207</v>
+        <v>13.69609638579286</v>
       </c>
       <c r="G124" t="n">
-        <v>12.95641931684334</v>
+        <v>13.16357828570605</v>
       </c>
       <c r="H124" t="n">
-        <v>8.480565371024735</v>
+        <v>8.496989063958893</v>
       </c>
       <c r="I124" t="n">
-        <v>8.00942285041225</v>
+        <v>7.59516712984504</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -4911,25 +4911,25 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>8.31353919239905</v>
+        <v>7.79840779515633</v>
       </c>
       <c r="E125" t="n">
-        <v>12.82660332541568</v>
+        <v>12.57494751399797</v>
       </c>
       <c r="F125" t="n">
-        <v>27.07838479809976</v>
+        <v>28.06811465069613</v>
       </c>
       <c r="G125" t="n">
-        <v>4.275534441805226</v>
+        <v>4.064581823422342</v>
       </c>
       <c r="H125" t="n">
-        <v>32.0665083135392</v>
+        <v>32.2351268913209</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>15.43942992874109</v>
+        <v>15.25882132540633</v>
       </c>
     </row>
     <row r="126">
@@ -4947,22 +4947,22 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>31.18686868686869</v>
+        <v>30.93759484245184</v>
       </c>
       <c r="E126" t="n">
-        <v>28.03030303030303</v>
+        <v>28.01106442595422</v>
       </c>
       <c r="F126" t="n">
-        <v>14.14141414141414</v>
+        <v>14.13066921093861</v>
       </c>
       <c r="G126" t="n">
-        <v>12.37373737373737</v>
+        <v>12.53654447003968</v>
       </c>
       <c r="H126" t="n">
-        <v>7.323232323232324</v>
+        <v>7.626963409527194</v>
       </c>
       <c r="I126" t="n">
-        <v>6.944444444444445</v>
+        <v>6.757163641088453</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -4983,25 +4983,25 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>4.578313253012048</v>
+        <v>4.76286622109594</v>
       </c>
       <c r="E127" t="n">
-        <v>15.42168674698795</v>
+        <v>14.78146169887695</v>
       </c>
       <c r="F127" t="n">
-        <v>26.50602409638554</v>
+        <v>27.44331016748887</v>
       </c>
       <c r="G127" t="n">
-        <v>4.096385542168675</v>
+        <v>3.983578196551005</v>
       </c>
       <c r="H127" t="n">
-        <v>29.87951807228916</v>
+        <v>30.52940361283595</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>19.51807228915663</v>
+        <v>18.4993801031513</v>
       </c>
     </row>
     <row r="128">
@@ -5019,22 +5019,22 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>26.82255845942229</v>
+        <v>27.37420771169899</v>
       </c>
       <c r="E128" t="n">
-        <v>24.62173314993122</v>
+        <v>25.14754501467337</v>
       </c>
       <c r="F128" t="n">
-        <v>16.36863823933975</v>
+        <v>15.91157551081633</v>
       </c>
       <c r="G128" t="n">
-        <v>13.61760660247593</v>
+        <v>13.63054688441558</v>
       </c>
       <c r="H128" t="n">
-        <v>10.31636863823934</v>
+        <v>10.10819545814849</v>
       </c>
       <c r="I128" t="n">
-        <v>8.253094910591471</v>
+        <v>7.827929420247232</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -5055,25 +5055,25 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>7.002801120448179</v>
+        <v>6.727355577223296</v>
       </c>
       <c r="E129" t="n">
-        <v>14.28571428571428</v>
+        <v>13.74706874350963</v>
       </c>
       <c r="F129" t="n">
-        <v>28.01120448179272</v>
+        <v>28.57890067893376</v>
       </c>
       <c r="G129" t="n">
-        <v>3.361344537815126</v>
+        <v>3.384571837686582</v>
       </c>
       <c r="H129" t="n">
-        <v>30.25210084033613</v>
+        <v>31.01815392454669</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>17.08683473389356</v>
+        <v>16.54394923810005</v>
       </c>
     </row>
     <row r="130">
@@ -5091,22 +5091,22 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>22.57250945775536</v>
+        <v>22.80594242097307</v>
       </c>
       <c r="E130" t="n">
-        <v>35.43505674653215</v>
+        <v>34.69439269855635</v>
       </c>
       <c r="F130" t="n">
-        <v>14.62799495586381</v>
+        <v>14.76545157840016</v>
       </c>
       <c r="G130" t="n">
-        <v>12.8625472887768</v>
+        <v>13.17799186167362</v>
       </c>
       <c r="H130" t="n">
-        <v>8.953341740226985</v>
+        <v>8.765247290001701</v>
       </c>
       <c r="I130" t="n">
-        <v>5.548549810844893</v>
+        <v>5.790974150395106</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -5127,25 +5127,25 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>5.76036866359447</v>
+        <v>5.583361411636504</v>
       </c>
       <c r="E131" t="n">
-        <v>14.51612903225807</v>
+        <v>14.32511172615864</v>
       </c>
       <c r="F131" t="n">
-        <v>28.57142857142857</v>
+        <v>27.9732951631294</v>
       </c>
       <c r="G131" t="n">
-        <v>5.069124423963133</v>
+        <v>4.746449449566654</v>
       </c>
       <c r="H131" t="n">
-        <v>23.27188940092166</v>
+        <v>24.11795704392864</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>22.8110599078341</v>
+        <v>23.25382520558017</v>
       </c>
     </row>
     <row r="132">
@@ -5163,22 +5163,22 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>26.4945652173913</v>
+        <v>26.17961589962154</v>
       </c>
       <c r="E132" t="n">
-        <v>28.66847826086957</v>
+        <v>29.30845751723652</v>
       </c>
       <c r="F132" t="n">
-        <v>16.71195652173913</v>
+        <v>16.37923874169772</v>
       </c>
       <c r="G132" t="n">
-        <v>11.54891304347826</v>
+        <v>12.03189609673501</v>
       </c>
       <c r="H132" t="n">
-        <v>8.016304347826086</v>
+        <v>7.845723278505027</v>
       </c>
       <c r="I132" t="n">
-        <v>8.559782608695652</v>
+        <v>8.255068466204197</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -5199,25 +5199,25 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>7.783018867924528</v>
+        <v>7.333914243602385</v>
       </c>
       <c r="E133" t="n">
-        <v>12.73584905660377</v>
+        <v>12.59379777433618</v>
       </c>
       <c r="F133" t="n">
-        <v>21.93396226415095</v>
+        <v>22.39840436790235</v>
       </c>
       <c r="G133" t="n">
-        <v>6.132075471698113</v>
+        <v>5.691296334462463</v>
       </c>
       <c r="H133" t="n">
-        <v>29.4811320754717</v>
+        <v>29.26445825235743</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>21.93396226415095</v>
+        <v>22.71812902733918</v>
       </c>
     </row>
     <row r="134">
@@ -5235,22 +5235,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>26.0047281323877</v>
+        <v>25.73310993564391</v>
       </c>
       <c r="E134" t="n">
-        <v>28.84160756501182</v>
+        <v>29.15217783689141</v>
       </c>
       <c r="F134" t="n">
-        <v>16.90307328605201</v>
+        <v>16.68193209843754</v>
       </c>
       <c r="G134" t="n">
-        <v>11.11111111111111</v>
+        <v>11.75148723730742</v>
       </c>
       <c r="H134" t="n">
-        <v>10.28368794326241</v>
+        <v>9.78681004945957</v>
       </c>
       <c r="I134" t="n">
-        <v>6.855791962174941</v>
+        <v>6.894482842260144</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -5271,25 +5271,25 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>7.218683651804671</v>
+        <v>6.8461669991237</v>
       </c>
       <c r="E135" t="n">
-        <v>8.280254777070063</v>
+        <v>8.975747635240685</v>
       </c>
       <c r="F135" t="n">
-        <v>29.723991507431</v>
+        <v>28.93169804056246</v>
       </c>
       <c r="G135" t="n">
-        <v>5.307855626326965</v>
+        <v>5.041195232177641</v>
       </c>
       <c r="H135" t="n">
-        <v>34.39490445859872</v>
+        <v>33.12834761078076</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>15.07430997876858</v>
+        <v>17.07684448211475</v>
       </c>
     </row>
     <row r="136">
@@ -5307,22 +5307,22 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>30.44943820224719</v>
+        <v>29.30124807571108</v>
       </c>
       <c r="E136" t="n">
-        <v>30.56179775280899</v>
+        <v>30.59834304040288</v>
       </c>
       <c r="F136" t="n">
-        <v>13.70786516853933</v>
+        <v>14.049377465551</v>
       </c>
       <c r="G136" t="n">
-        <v>10.67415730337079</v>
+        <v>11.40596140774632</v>
       </c>
       <c r="H136" t="n">
-        <v>6.292134831460674</v>
+        <v>6.61443243662561</v>
       </c>
       <c r="I136" t="n">
-        <v>8.314606741573034</v>
+        <v>8.030637573963103</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -5343,25 +5343,25 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>8.086785009861932</v>
+        <v>7.580990454822395</v>
       </c>
       <c r="E137" t="n">
-        <v>10.6508875739645</v>
+        <v>10.85130022576011</v>
       </c>
       <c r="F137" t="n">
-        <v>23.86587771203156</v>
+        <v>24.22596490201293</v>
       </c>
       <c r="G137" t="n">
-        <v>5.522682445759369</v>
+        <v>5.108687279082766</v>
       </c>
       <c r="H137" t="n">
-        <v>29.98027613412228</v>
+        <v>29.60802002517883</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>21.89349112426036</v>
+        <v>22.62503711314298</v>
       </c>
     </row>
     <row r="138">
@@ -5379,22 +5379,22 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>25.23364485981308</v>
+        <v>25.23529637616367</v>
       </c>
       <c r="E138" t="n">
-        <v>30.95794392523364</v>
+        <v>31.0216095843592</v>
       </c>
       <c r="F138" t="n">
-        <v>16.9392523364486</v>
+        <v>16.56580116847395</v>
       </c>
       <c r="G138" t="n">
-        <v>12.5</v>
+        <v>12.91002931767538</v>
       </c>
       <c r="H138" t="n">
-        <v>7.009345794392523</v>
+        <v>7.004518284749913</v>
       </c>
       <c r="I138" t="n">
-        <v>7.359813084112149</v>
+        <v>7.262745268577894</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -5415,25 +5415,25 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>9.825327510917029</v>
+        <v>9.029373306137016</v>
       </c>
       <c r="E139" t="n">
-        <v>13.31877729257642</v>
+        <v>13.36597987992986</v>
       </c>
       <c r="F139" t="n">
-        <v>26.20087336244541</v>
+        <v>25.90900890134527</v>
       </c>
       <c r="G139" t="n">
-        <v>4.803493449781659</v>
+        <v>4.561020033313111</v>
       </c>
       <c r="H139" t="n">
-        <v>27.7292576419214</v>
+        <v>27.45824309240006</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>18.12227074235808</v>
+        <v>19.67637478687469</v>
       </c>
     </row>
     <row r="140">
@@ -5451,22 +5451,22 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>21.65397170837867</v>
+        <v>22.2119227436118</v>
       </c>
       <c r="E140" t="n">
-        <v>33.40587595212187</v>
+        <v>32.93088903073971</v>
       </c>
       <c r="F140" t="n">
-        <v>15.01632208922742</v>
+        <v>15.125270622863</v>
       </c>
       <c r="G140" t="n">
-        <v>13.92818280739935</v>
+        <v>13.95782945496659</v>
       </c>
       <c r="H140" t="n">
-        <v>8.269858541893363</v>
+        <v>8.201688541999834</v>
       </c>
       <c r="I140" t="n">
-        <v>7.725788900979326</v>
+        <v>7.572399605819051</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -5487,25 +5487,25 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>6.237424547283702</v>
+        <v>6.067655135500326</v>
       </c>
       <c r="E141" t="n">
-        <v>15.49295774647887</v>
+        <v>15.39680422847276</v>
       </c>
       <c r="F141" t="n">
-        <v>25.35211267605634</v>
+        <v>25.29586025820683</v>
       </c>
       <c r="G141" t="n">
-        <v>5.835010060362174</v>
+        <v>5.373753585151614</v>
       </c>
       <c r="H141" t="n">
-        <v>29.97987927565392</v>
+        <v>29.24059735572829</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>17.10261569416499</v>
+        <v>18.62532943694017</v>
       </c>
     </row>
     <row r="142">
@@ -5523,22 +5523,22 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>24.29378531073446</v>
+        <v>24.35411387054633</v>
       </c>
       <c r="E142" t="n">
-        <v>32.67419962335217</v>
+        <v>32.08967094358979</v>
       </c>
       <c r="F142" t="n">
-        <v>16.94915254237288</v>
+        <v>16.89359405471797</v>
       </c>
       <c r="G142" t="n">
-        <v>11.20527306967985</v>
+        <v>11.87197568137359</v>
       </c>
       <c r="H142" t="n">
-        <v>7.909604519774012</v>
+        <v>7.878036706859002</v>
       </c>
       <c r="I142" t="n">
-        <v>6.96798493408663</v>
+        <v>6.912608742913334</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -5559,25 +5559,25 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>6.401384083044983</v>
+        <v>6.170509237263232</v>
       </c>
       <c r="E143" t="n">
-        <v>9.515570934256056</v>
+        <v>10.32807923847769</v>
       </c>
       <c r="F143" t="n">
-        <v>22.14532871972319</v>
+        <v>22.76229418651237</v>
       </c>
       <c r="G143" t="n">
-        <v>4.671280276816609</v>
+        <v>4.44887861305564</v>
       </c>
       <c r="H143" t="n">
-        <v>34.77508650519031</v>
+        <v>33.31630595887912</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>22.49134948096886</v>
+        <v>22.97393276581196</v>
       </c>
     </row>
     <row r="144">
@@ -5595,22 +5595,22 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>28.42105263157895</v>
+        <v>27.81952173784407</v>
       </c>
       <c r="E144" t="n">
-        <v>29.2822966507177</v>
+        <v>29.54240477212993</v>
       </c>
       <c r="F144" t="n">
-        <v>15.11961722488038</v>
+        <v>15.24622499561497</v>
       </c>
       <c r="G144" t="n">
-        <v>10.52631578947368</v>
+        <v>11.27487954401728</v>
       </c>
       <c r="H144" t="n">
-        <v>8.899521531100477</v>
+        <v>8.552393680841115</v>
       </c>
       <c r="I144" t="n">
-        <v>7.751196172248803</v>
+        <v>7.564575269552631</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -5631,25 +5631,25 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>5.783582089552239</v>
+        <v>5.666498124129089</v>
       </c>
       <c r="E145" t="n">
-        <v>12.3134328358209</v>
+        <v>12.4690180770668</v>
       </c>
       <c r="F145" t="n">
-        <v>25.37313432835821</v>
+        <v>25.37770896084832</v>
       </c>
       <c r="G145" t="n">
-        <v>3.731343283582089</v>
+        <v>3.592010557661072</v>
       </c>
       <c r="H145" t="n">
-        <v>34.51492537313433</v>
+        <v>33.53632168226256</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>18.28358208955224</v>
+        <v>19.35844259803216</v>
       </c>
     </row>
     <row r="146">
@@ -5667,22 +5667,22 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>24.94085839810747</v>
+        <v>24.63341117550176</v>
       </c>
       <c r="E146" t="n">
-        <v>32.44339303818858</v>
+        <v>31.74235023776601</v>
       </c>
       <c r="F146" t="n">
-        <v>15.27543088881379</v>
+        <v>15.41977164632082</v>
       </c>
       <c r="G146" t="n">
-        <v>11.99729638391348</v>
+        <v>12.72341596802666</v>
       </c>
       <c r="H146" t="n">
-        <v>8.009462656302805</v>
+        <v>8.19597986566033</v>
       </c>
       <c r="I146" t="n">
-        <v>7.333558634673876</v>
+        <v>7.28507110672441</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -5703,25 +5703,25 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>9.415584415584416</v>
+        <v>8.928182406361792</v>
       </c>
       <c r="E147" t="n">
-        <v>12.07792207792208</v>
+        <v>11.86330427483921</v>
       </c>
       <c r="F147" t="n">
-        <v>24.87012987012987</v>
+        <v>25.11879346129711</v>
       </c>
       <c r="G147" t="n">
-        <v>4.675324675324675</v>
+        <v>4.713235705020218</v>
       </c>
       <c r="H147" t="n">
-        <v>28.63636363636364</v>
+        <v>29.82912674719341</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>20.32467532467533</v>
+        <v>19.54735740528826</v>
       </c>
     </row>
     <row r="148">
@@ -5739,22 +5739,22 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>29.43132690389092</v>
+        <v>28.29486786578596</v>
       </c>
       <c r="E148" t="n">
-        <v>26.20552045227802</v>
+        <v>26.60241592452823</v>
       </c>
       <c r="F148" t="n">
-        <v>17.95809777186565</v>
+        <v>17.6443014198484</v>
       </c>
       <c r="G148" t="n">
-        <v>12.60392417692052</v>
+        <v>13.16531318008944</v>
       </c>
       <c r="H148" t="n">
-        <v>7.016960425673428</v>
+        <v>7.438122462360488</v>
       </c>
       <c r="I148" t="n">
-        <v>6.784170269371466</v>
+        <v>6.854979147387485</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -5775,25 +5775,25 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>6.879299562226391</v>
+        <v>6.82228677099868</v>
       </c>
       <c r="E149" t="n">
-        <v>10.63164477798624</v>
+        <v>10.511788279274</v>
       </c>
       <c r="F149" t="n">
-        <v>27.70481550969356</v>
+        <v>26.95175620623458</v>
       </c>
       <c r="G149" t="n">
-        <v>5.190744215134459</v>
+        <v>5.168694993188442</v>
       </c>
       <c r="H149" t="n">
-        <v>32.89555972482802</v>
+        <v>33.92170502057776</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>16.69793621013133</v>
+        <v>16.62376872972654</v>
       </c>
     </row>
     <row r="150">
@@ -5811,22 +5811,22 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>29.9560680944536</v>
+        <v>28.73393534265777</v>
       </c>
       <c r="E150" t="n">
-        <v>27.95167490389895</v>
+        <v>28.14501191627501</v>
       </c>
       <c r="F150" t="n">
-        <v>16.41954969796815</v>
+        <v>16.43472533756903</v>
       </c>
       <c r="G150" t="n">
-        <v>10.79077429983526</v>
+        <v>11.60422565340117</v>
       </c>
       <c r="H150" t="n">
-        <v>7.358594179022515</v>
+        <v>7.678769241734519</v>
       </c>
       <c r="I150" t="n">
-        <v>7.523338824821526</v>
+        <v>7.403332508362503</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -5847,25 +5847,25 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>6.337687469762941</v>
+        <v>6.427802363854981</v>
       </c>
       <c r="E151" t="n">
-        <v>12.14320270924045</v>
+        <v>11.69884023595848</v>
       </c>
       <c r="F151" t="n">
-        <v>27.57619738751814</v>
+        <v>26.76077931299755</v>
       </c>
       <c r="G151" t="n">
-        <v>5.902273826802128</v>
+        <v>5.801127377581969</v>
       </c>
       <c r="H151" t="n">
-        <v>28.5921625544267</v>
+        <v>30.46318571343186</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>19.44847605224964</v>
+        <v>18.84826499617517</v>
       </c>
     </row>
     <row r="152">
@@ -5883,22 +5883,22 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>25.92471358428805</v>
+        <v>25.68984340409993</v>
       </c>
       <c r="E152" t="n">
-        <v>26.18657937806874</v>
+        <v>26.27464620623815</v>
       </c>
       <c r="F152" t="n">
-        <v>16.33387888707038</v>
+        <v>16.21748153153169</v>
       </c>
       <c r="G152" t="n">
-        <v>14.72995090016367</v>
+        <v>14.96567144968375</v>
       </c>
       <c r="H152" t="n">
-        <v>8.936170212765958</v>
+        <v>9.070296029295895</v>
       </c>
       <c r="I152" t="n">
-        <v>7.888707037643209</v>
+        <v>7.782061379150583</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -5919,25 +5919,25 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>5.324459234608985</v>
+        <v>5.584236661296939</v>
       </c>
       <c r="E153" t="n">
-        <v>11.5363283416528</v>
+        <v>11.32889637493705</v>
       </c>
       <c r="F153" t="n">
-        <v>23.90460343871326</v>
+        <v>23.89330426262424</v>
       </c>
       <c r="G153" t="n">
-        <v>4.769828064337216</v>
+        <v>4.802728136928766</v>
       </c>
       <c r="H153" t="n">
-        <v>36.82750970604548</v>
+        <v>37.03144262808188</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>17.63727121464226</v>
+        <v>17.35939193613111</v>
       </c>
     </row>
     <row r="154">
@@ -5955,22 +5955,22 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>23.89148191365228</v>
+        <v>23.78640904822313</v>
       </c>
       <c r="E154" t="n">
-        <v>31.85530921820303</v>
+        <v>31.12562669255824</v>
       </c>
       <c r="F154" t="n">
-        <v>17.44457409568261</v>
+        <v>17.2577127870357</v>
       </c>
       <c r="G154" t="n">
-        <v>10.3267211201867</v>
+        <v>11.32174238057026</v>
       </c>
       <c r="H154" t="n">
-        <v>8.634772462077013</v>
+        <v>8.796633592205499</v>
       </c>
       <c r="I154" t="n">
-        <v>7.847141190198366</v>
+        <v>7.711875499407168</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -5991,25 +5991,25 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>5.879586077140169</v>
+        <v>5.998552685069044</v>
       </c>
       <c r="E155" t="n">
-        <v>11.80620884289746</v>
+        <v>11.5632982651675</v>
       </c>
       <c r="F155" t="n">
-        <v>27.61053621825024</v>
+        <v>27.15770706822042</v>
       </c>
       <c r="G155" t="n">
-        <v>3.80997177798683</v>
+        <v>4.028516663766935</v>
       </c>
       <c r="H155" t="n">
-        <v>32.97271872060207</v>
+        <v>33.62309492178581</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>17.92097836312324</v>
+        <v>17.62883039599029</v>
       </c>
     </row>
     <row r="156">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>25.99118942731278</v>
+        <v>25.60393875098816</v>
       </c>
       <c r="E156" t="n">
-        <v>31.69214822492874</v>
+        <v>31.01725855856077</v>
       </c>
       <c r="F156" t="n">
-        <v>15.02980046644208</v>
+        <v>15.17694154184199</v>
       </c>
       <c r="G156" t="n">
-        <v>13.88960870691889</v>
+        <v>14.22819175059211</v>
       </c>
       <c r="H156" t="n">
-        <v>7.255765742420316</v>
+        <v>7.639405655740382</v>
       </c>
       <c r="I156" t="n">
-        <v>6.141487431977196</v>
+        <v>6.334263742276594</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -6063,25 +6063,25 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>6.758080313418217</v>
+        <v>6.730383916290954</v>
       </c>
       <c r="E157" t="n">
-        <v>9.892262487757101</v>
+        <v>9.999295760458182</v>
       </c>
       <c r="F157" t="n">
-        <v>26.05288932419197</v>
+        <v>25.78369045687245</v>
       </c>
       <c r="G157" t="n">
-        <v>4.603330068560235</v>
+        <v>4.679013728309646</v>
       </c>
       <c r="H157" t="n">
-        <v>34.37806072477963</v>
+        <v>34.82488486367396</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>18.31537708129285</v>
+        <v>17.9827312743948</v>
       </c>
     </row>
     <row r="158">
@@ -6099,22 +6099,22 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>29.91250886734453</v>
+        <v>28.89709879504971</v>
       </c>
       <c r="E158" t="n">
-        <v>25.75076850319224</v>
+        <v>26.1383176675716</v>
       </c>
       <c r="F158" t="n">
-        <v>15.2754788366044</v>
+        <v>15.39113995248544</v>
       </c>
       <c r="G158" t="n">
-        <v>12.8162686214235</v>
+        <v>13.30457089956402</v>
       </c>
       <c r="H158" t="n">
-        <v>7.992433199337905</v>
+        <v>8.208739570984809</v>
       </c>
       <c r="I158" t="n">
-        <v>8.252541972097422</v>
+        <v>8.060133114344428</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -6135,25 +6135,25 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>6.777251184834124</v>
+        <v>6.767148600954698</v>
       </c>
       <c r="E159" t="n">
-        <v>10.90047393364929</v>
+        <v>10.76109040462061</v>
       </c>
       <c r="F159" t="n">
-        <v>29.57345971563981</v>
+        <v>28.4547555806811</v>
       </c>
       <c r="G159" t="n">
-        <v>3.649289099526067</v>
+        <v>3.916424013074739</v>
       </c>
       <c r="H159" t="n">
-        <v>30.42654028436019</v>
+        <v>31.87776351903996</v>
       </c>
       <c r="I159" t="n">
         <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>18.67298578199052</v>
+        <v>18.2228178816289</v>
       </c>
     </row>
     <row r="160">
@@ -6171,22 +6171,22 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>26.50826927556487</v>
+        <v>25.93383692607703</v>
       </c>
       <c r="E160" t="n">
-        <v>30.53808525506639</v>
+        <v>30.14593253220096</v>
       </c>
       <c r="F160" t="n">
-        <v>15.23410202655486</v>
+        <v>15.51578187847861</v>
       </c>
       <c r="G160" t="n">
-        <v>12.81155369205684</v>
+        <v>13.29305352203514</v>
       </c>
       <c r="H160" t="n">
-        <v>8.502212904728628</v>
+        <v>8.576029980835663</v>
       </c>
       <c r="I160" t="n">
-        <v>6.405776846028418</v>
+        <v>6.535365160372593</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -6207,25 +6207,25 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>5.356389708983551</v>
+        <v>5.589940211971197</v>
       </c>
       <c r="E161" t="n">
-        <v>10.58625052720371</v>
+        <v>10.53375578455448</v>
       </c>
       <c r="F161" t="n">
-        <v>29.10164487557993</v>
+        <v>28.16446397893539</v>
       </c>
       <c r="G161" t="n">
-        <v>4.175453395191902</v>
+        <v>4.356594433006982</v>
       </c>
       <c r="H161" t="n">
-        <v>33.10839308308731</v>
+        <v>33.89586930788883</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>17.67186840995361</v>
+        <v>17.45937628364313</v>
       </c>
     </row>
     <row r="162">
@@ -6243,22 +6243,22 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>28.97099447513812</v>
+        <v>28.07576290209359</v>
       </c>
       <c r="E162" t="n">
-        <v>26.60566298342541</v>
+        <v>27.64243070735901</v>
       </c>
       <c r="F162" t="n">
-        <v>16.10842541436464</v>
+        <v>15.97243413779642</v>
       </c>
       <c r="G162" t="n">
-        <v>12.37914364640884</v>
+        <v>12.20845328404676</v>
       </c>
       <c r="H162" t="n">
-        <v>8.926104972375692</v>
+        <v>9.023718391930277</v>
       </c>
       <c r="I162" t="n">
-        <v>7.009668508287293</v>
+        <v>7.077200576773941</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -6279,25 +6279,25 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>6.811509101585438</v>
+        <v>6.718929792316469</v>
       </c>
       <c r="E163" t="n">
-        <v>12.59541984732824</v>
+        <v>13.11310956874108</v>
       </c>
       <c r="F163" t="n">
-        <v>28.15619495008808</v>
+        <v>27.35042503041136</v>
       </c>
       <c r="G163" t="n">
-        <v>5.372871403405755</v>
+        <v>5.307957305257603</v>
       </c>
       <c r="H163" t="n">
-        <v>32.58954785672343</v>
+        <v>32.43746549950628</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>14.47445684086905</v>
+        <v>15.07211280376721</v>
       </c>
     </row>
     <row r="164">
@@ -6315,22 +6315,22 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>25.47361828714577</v>
+        <v>25.2323151071025</v>
       </c>
       <c r="E164" t="n">
-        <v>29.56004383904807</v>
+        <v>29.99212304276118</v>
       </c>
       <c r="F164" t="n">
-        <v>15.84468451542195</v>
+        <v>15.76630370784666</v>
       </c>
       <c r="G164" t="n">
-        <v>12.6506967277282</v>
+        <v>12.52432045868784</v>
       </c>
       <c r="H164" t="n">
-        <v>8.298105526851417</v>
+        <v>8.502998375618077</v>
       </c>
       <c r="I164" t="n">
-        <v>8.172851103804604</v>
+        <v>7.981939307983748</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -6351,25 +6351,25 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>6.357388316151202</v>
+        <v>6.340889949404495</v>
       </c>
       <c r="E165" t="n">
-        <v>13.00114547537228</v>
+        <v>13.38279902024005</v>
       </c>
       <c r="F165" t="n">
-        <v>24.65635738831615</v>
+        <v>24.79573489022938</v>
       </c>
       <c r="G165" t="n">
-        <v>5.06872852233677</v>
+        <v>5.084607424646865</v>
       </c>
       <c r="H165" t="n">
-        <v>33.90607101947308</v>
+        <v>33.40989478503717</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>17.01030927835052</v>
+        <v>16.98607393044203</v>
       </c>
     </row>
     <row r="166">
@@ -6387,22 +6387,22 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>27.15578847070033</v>
+        <v>26.99714922397718</v>
       </c>
       <c r="E166" t="n">
-        <v>33.22216928696204</v>
+        <v>33.11249134948444</v>
       </c>
       <c r="F166" t="n">
-        <v>14.38780371605526</v>
+        <v>14.39988168249496</v>
       </c>
       <c r="G166" t="n">
-        <v>12.22804510084167</v>
+        <v>12.0357614373043</v>
       </c>
       <c r="H166" t="n">
-        <v>6.241067174845164</v>
+        <v>6.711500381872226</v>
       </c>
       <c r="I166" t="n">
-        <v>6.765126250595522</v>
+        <v>6.743215924866895</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -6423,25 +6423,25 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6.600846262341325</v>
+        <v>6.604945199987693</v>
       </c>
       <c r="E167" t="n">
-        <v>14.18899858956276</v>
+        <v>14.60564983064991</v>
       </c>
       <c r="F167" t="n">
-        <v>22.76445698166432</v>
+        <v>22.8005009757577</v>
       </c>
       <c r="G167" t="n">
-        <v>4.880112834978843</v>
+        <v>4.983090767914934</v>
       </c>
       <c r="H167" t="n">
-        <v>33.31452750352609</v>
+        <v>32.87384142837806</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>18.25105782792665</v>
+        <v>18.13197179731171</v>
       </c>
     </row>
     <row r="168">
@@ -6459,22 +6459,22 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>24.93120528343423</v>
+        <v>24.95710334306929</v>
       </c>
       <c r="E168" t="n">
-        <v>34.08090258668135</v>
+        <v>33.88596073439637</v>
       </c>
       <c r="F168" t="n">
-        <v>15.60264171711612</v>
+        <v>15.47011674456577</v>
       </c>
       <c r="G168" t="n">
-        <v>10.51183269124931</v>
+        <v>10.59231953557628</v>
       </c>
       <c r="H168" t="n">
-        <v>7.278481012658228</v>
+        <v>7.593057294084401</v>
       </c>
       <c r="I168" t="n">
-        <v>7.59493670886076</v>
+        <v>7.501442348307885</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -6495,25 +6495,25 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>5.904455179817498</v>
+        <v>5.964187574839257</v>
       </c>
       <c r="E169" t="n">
-        <v>14.78797638217928</v>
+        <v>14.87467555279131</v>
       </c>
       <c r="F169" t="n">
-        <v>25.20128824476651</v>
+        <v>25.06960091811182</v>
       </c>
       <c r="G169" t="n">
-        <v>4.26731078904992</v>
+        <v>4.449553292463087</v>
       </c>
       <c r="H169" t="n">
-        <v>31.29361245303274</v>
+        <v>31.28565389937507</v>
       </c>
       <c r="I169" t="n">
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>18.54535695115405</v>
+        <v>18.35632876241945</v>
       </c>
     </row>
     <row r="170">
@@ -6531,22 +6531,22 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>28.7429281081827</v>
+        <v>28.18592022061385</v>
       </c>
       <c r="E170" t="n">
-        <v>30.60576790396026</v>
+        <v>30.90598023299147</v>
       </c>
       <c r="F170" t="n">
-        <v>14.64054091348144</v>
+        <v>14.66054644102253</v>
       </c>
       <c r="G170" t="n">
-        <v>11.2322340278736</v>
+        <v>11.23981782148993</v>
       </c>
       <c r="H170" t="n">
-        <v>8.29308679453567</v>
+        <v>8.457033008057779</v>
       </c>
       <c r="I170" t="n">
-        <v>6.48544225196633</v>
+        <v>6.550702275824428</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -6567,25 +6567,25 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>5.845258307057968</v>
+        <v>5.890066801538916</v>
       </c>
       <c r="E171" t="n">
-        <v>13.65510550569973</v>
+        <v>14.00327300446556</v>
       </c>
       <c r="F171" t="n">
-        <v>26.77661896677177</v>
+        <v>26.48177879687322</v>
       </c>
       <c r="G171" t="n">
-        <v>4.244482173174872</v>
+        <v>4.359391771220242</v>
       </c>
       <c r="H171" t="n">
-        <v>30.53601746301237</v>
+        <v>30.52959483661732</v>
       </c>
       <c r="I171" t="n">
         <v>0</v>
       </c>
       <c r="J171" t="n">
-        <v>18.94251758428329</v>
+        <v>18.73589478928473</v>
       </c>
     </row>
     <row r="172">
@@ -6603,22 +6603,22 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>22.76843467011643</v>
+        <v>23.15682363377097</v>
       </c>
       <c r="E172" t="n">
-        <v>32.54851228978008</v>
+        <v>32.43669839325521</v>
       </c>
       <c r="F172" t="n">
-        <v>16.54592496765847</v>
+        <v>16.34826677807602</v>
       </c>
       <c r="G172" t="n">
-        <v>12.6261319534282</v>
+        <v>12.45730846631603</v>
       </c>
       <c r="H172" t="n">
-        <v>8.072445019404915</v>
+        <v>8.264812025937685</v>
       </c>
       <c r="I172" t="n">
-        <v>7.438551099611902</v>
+        <v>7.336090702644095</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -6639,25 +6639,25 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>6.213553187210939</v>
+        <v>6.194114393186548</v>
       </c>
       <c r="E173" t="n">
-        <v>13.05047255177961</v>
+        <v>13.42490995749532</v>
       </c>
       <c r="F173" t="n">
-        <v>29.35853609491253</v>
+        <v>28.49115635041807</v>
       </c>
       <c r="G173" t="n">
-        <v>4.564649105167907</v>
+        <v>4.69237269183384</v>
       </c>
       <c r="H173" t="n">
-        <v>31.57048059521416</v>
+        <v>31.59196233739299</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>15.24230846571486</v>
+        <v>15.60548426967322</v>
       </c>
     </row>
     <row r="174">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>24.82929857231533</v>
+        <v>24.84954728523995</v>
       </c>
       <c r="E174" t="n">
-        <v>33.22160148975792</v>
+        <v>32.89357050011238</v>
       </c>
       <c r="F174" t="n">
-        <v>14.252017380509</v>
+        <v>14.47965775838378</v>
       </c>
       <c r="G174" t="n">
-        <v>12.26567349472377</v>
+        <v>12.10535102957025</v>
       </c>
       <c r="H174" t="n">
-        <v>8.950962135319678</v>
+        <v>9.076782824045905</v>
       </c>
       <c r="I174" t="n">
-        <v>6.480446927374302</v>
+        <v>6.59509060264775</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -6711,25 +6711,25 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>7.714561234329798</v>
+        <v>7.496664878500366</v>
       </c>
       <c r="E175" t="n">
-        <v>13.1870781099325</v>
+        <v>13.52484011590549</v>
       </c>
       <c r="F175" t="n">
-        <v>20.10607521697204</v>
+        <v>20.80027357053063</v>
       </c>
       <c r="G175" t="n">
-        <v>5.665380906460945</v>
+        <v>5.566941360277604</v>
       </c>
       <c r="H175" t="n">
-        <v>31.55737704918033</v>
+        <v>31.52467901405365</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>21.7695274831244</v>
+        <v>21.08660106073226</v>
       </c>
     </row>
     <row r="176">
@@ -6747,22 +6747,22 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>27.03504966320357</v>
+        <v>26.62927890710232</v>
       </c>
       <c r="E176" t="n">
-        <v>29.26133120219203</v>
+        <v>29.73894436796086</v>
       </c>
       <c r="F176" t="n">
-        <v>16.50873387372988</v>
+        <v>16.32077310055979</v>
       </c>
       <c r="G176" t="n">
-        <v>10.76606918598013</v>
+        <v>10.93983266711165</v>
       </c>
       <c r="H176" t="n">
-        <v>8.49412033337139</v>
+        <v>8.592487988070324</v>
       </c>
       <c r="I176" t="n">
-        <v>7.934695741523005</v>
+        <v>7.778682969195053</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -6783,25 +6783,25 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>7.836846929422549</v>
+        <v>7.590739094095566</v>
       </c>
       <c r="E177" t="n">
-        <v>11.82401466544455</v>
+        <v>12.44265457817498</v>
       </c>
       <c r="F177" t="n">
-        <v>20.66911090742438</v>
+        <v>21.18105626499568</v>
       </c>
       <c r="G177" t="n">
-        <v>4.101741521539871</v>
+        <v>4.306273093956519</v>
       </c>
       <c r="H177" t="n">
-        <v>35.01374885426215</v>
+        <v>34.43728205635387</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>20.55453712190651</v>
+        <v>20.0419949124234</v>
       </c>
     </row>
   </sheetData>
